--- a/apps/snapshot/keepa_us_to_jp_cross_asin/brand/brand_recheck_all.xlsx
+++ b/apps/snapshot/keepa_us_to_jp_cross_asin/brand/brand_recheck_all.xlsx
@@ -69104,11 +69104,19 @@
           <t>B0F6LDDNBT</t>
         </is>
       </c>
-      <c r="D2147" t="inlineStr"/>
-      <c r="E2147" t="inlineStr"/>
+      <c r="D2147" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2147" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -69128,11 +69136,19 @@
           <t>B0F6LNCGG8</t>
         </is>
       </c>
-      <c r="D2148" t="inlineStr"/>
-      <c r="E2148" t="inlineStr"/>
+      <c r="D2148" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2148" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -69152,11 +69168,19 @@
           <t>B0F6LVM3RN</t>
         </is>
       </c>
-      <c r="D2149" t="inlineStr"/>
-      <c r="E2149" t="inlineStr"/>
+      <c r="D2149" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2149" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -69176,11 +69200,19 @@
           <t>B0F6LX4Z8P</t>
         </is>
       </c>
-      <c r="D2150" t="inlineStr"/>
-      <c r="E2150" t="inlineStr"/>
+      <c r="D2150" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2150" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -69200,11 +69232,19 @@
           <t>B0F6LXHVTD</t>
         </is>
       </c>
-      <c r="D2151" t="inlineStr"/>
-      <c r="E2151" t="inlineStr"/>
+      <c r="D2151" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2151" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -69224,11 +69264,19 @@
           <t>B0F6LY33V8</t>
         </is>
       </c>
-      <c r="D2152" t="inlineStr"/>
-      <c r="E2152" t="inlineStr"/>
+      <c r="D2152" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2152" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -69248,11 +69296,19 @@
           <t>B0F6LYFJTM</t>
         </is>
       </c>
-      <c r="D2153" t="inlineStr"/>
-      <c r="E2153" t="inlineStr"/>
+      <c r="D2153" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2153" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -69272,11 +69328,19 @@
           <t>B0F6LZBM7Y</t>
         </is>
       </c>
-      <c r="D2154" t="inlineStr"/>
-      <c r="E2154" t="inlineStr"/>
+      <c r="D2154" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2154" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -69296,11 +69360,19 @@
           <t>B0F6M11PLV</t>
         </is>
       </c>
-      <c r="D2155" t="inlineStr"/>
-      <c r="E2155" t="inlineStr"/>
+      <c r="D2155" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2155" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -69320,11 +69392,19 @@
           <t>B0F6NDJZ29</t>
         </is>
       </c>
-      <c r="D2156" t="inlineStr"/>
-      <c r="E2156" t="inlineStr"/>
+      <c r="D2156" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2156" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -69344,11 +69424,19 @@
           <t>B0F6NMYPPP</t>
         </is>
       </c>
-      <c r="D2157" t="inlineStr"/>
-      <c r="E2157" t="inlineStr"/>
+      <c r="D2157" t="inlineStr">
+        <is>
+          <t>大黒摩季 形式: CD</t>
+        </is>
+      </c>
+      <c r="E2157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2157" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -69368,11 +69456,19 @@
           <t>B0F6XL6LM7</t>
         </is>
       </c>
-      <c r="D2158" t="inlineStr"/>
-      <c r="E2158" t="inlineStr"/>
+      <c r="D2158" t="inlineStr">
+        <is>
+          <t>AOC</t>
+        </is>
+      </c>
+      <c r="E2158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2158" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -69392,11 +69488,19 @@
           <t>B0F6YS8DTB</t>
         </is>
       </c>
-      <c r="D2159" t="inlineStr"/>
-      <c r="E2159" t="inlineStr"/>
+      <c r="D2159" t="inlineStr">
+        <is>
+          <t>BINHENGLON</t>
+        </is>
+      </c>
+      <c r="E2159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2159" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -69416,11 +69520,19 @@
           <t>B0F7GSCV7S</t>
         </is>
       </c>
-      <c r="D2160" t="inlineStr"/>
-      <c r="E2160" t="inlineStr"/>
+      <c r="D2160" t="inlineStr">
+        <is>
+          <t>- (出演) 形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2160" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -69440,11 +69552,19 @@
           <t>B0F7GVXZMY</t>
         </is>
       </c>
-      <c r="D2161" t="inlineStr"/>
-      <c r="E2161" t="inlineStr"/>
+      <c r="D2161" t="inlineStr">
+        <is>
+          <t>- (出演) 形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2161" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -69464,11 +69584,19 @@
           <t>B0F7J2P4TH</t>
         </is>
       </c>
-      <c r="D2162" t="inlineStr"/>
-      <c r="E2162" t="inlineStr"/>
+      <c r="D2162" t="inlineStr">
+        <is>
+          <t>aimuonos</t>
+        </is>
+      </c>
+      <c r="E2162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2162" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -69488,11 +69616,19 @@
           <t>B0F7J54214</t>
         </is>
       </c>
-      <c r="D2163" t="inlineStr"/>
-      <c r="E2163" t="inlineStr"/>
+      <c r="D2163" t="inlineStr">
+        <is>
+          <t>aimuonos</t>
+        </is>
+      </c>
+      <c r="E2163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2163" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -69512,11 +69648,19 @@
           <t>B0F7JTCZSD</t>
         </is>
       </c>
-      <c r="D2164" t="inlineStr"/>
-      <c r="E2164" t="inlineStr"/>
+      <c r="D2164" t="inlineStr">
+        <is>
+          <t>AlicHome</t>
+        </is>
+      </c>
+      <c r="E2164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2164" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -69536,11 +69680,19 @@
           <t>B0F7L4VHR2</t>
         </is>
       </c>
-      <c r="D2165" t="inlineStr"/>
-      <c r="E2165" t="inlineStr"/>
+      <c r="D2165" t="inlineStr">
+        <is>
+          <t>MyDual</t>
+        </is>
+      </c>
+      <c r="E2165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2165" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -69560,11 +69712,19 @@
           <t>B0F7X232Y2</t>
         </is>
       </c>
-      <c r="D2166" t="inlineStr"/>
-      <c r="E2166" t="inlineStr"/>
+      <c r="D2166" t="inlineStr">
+        <is>
+          <t>ZPUJIU</t>
+        </is>
+      </c>
+      <c r="E2166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2166" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -69584,11 +69744,19 @@
           <t>B0F7X31Q21</t>
         </is>
       </c>
-      <c r="D2167" t="inlineStr"/>
-      <c r="E2167" t="inlineStr"/>
+      <c r="D2167" t="inlineStr">
+        <is>
+          <t>Areden</t>
+        </is>
+      </c>
+      <c r="E2167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2167" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -69608,11 +69776,19 @@
           <t>B0F7X6QT91</t>
         </is>
       </c>
-      <c r="D2168" t="inlineStr"/>
-      <c r="E2168" t="inlineStr"/>
+      <c r="D2168" t="inlineStr">
+        <is>
+          <t>高中正義 (出演) 形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2168" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -69632,11 +69808,19 @@
           <t>B0F83VBHS7</t>
         </is>
       </c>
-      <c r="D2169" t="inlineStr"/>
-      <c r="E2169" t="inlineStr"/>
+      <c r="D2169" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2169" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -69656,11 +69840,19 @@
           <t>B0F849W3Z3</t>
         </is>
       </c>
-      <c r="D2170" t="inlineStr"/>
-      <c r="E2170" t="inlineStr"/>
+      <c r="D2170" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="E2170" t="inlineStr">
+        <is>
+          <t>判定不能</t>
+        </is>
+      </c>
       <c r="F2170" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -69680,11 +69872,19 @@
           <t>B0F84CVKFR</t>
         </is>
       </c>
-      <c r="D2171" t="inlineStr"/>
-      <c r="E2171" t="inlineStr"/>
+      <c r="D2171" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2171" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -69704,11 +69904,19 @@
           <t>B0F84D8YCF</t>
         </is>
       </c>
-      <c r="D2172" t="inlineStr"/>
-      <c r="E2172" t="inlineStr"/>
+      <c r="D2172" t="inlineStr">
+        <is>
+          <t>椿屋四重奏 (出演) 形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2172" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -69728,11 +69936,19 @@
           <t>B0F84F9CG4</t>
         </is>
       </c>
-      <c r="D2173" t="inlineStr"/>
-      <c r="E2173" t="inlineStr"/>
+      <c r="D2173" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2173" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -69752,11 +69968,19 @@
           <t>B0F8B36FLS</t>
         </is>
       </c>
-      <c r="D2174" t="inlineStr"/>
-      <c r="E2174" t="inlineStr"/>
+      <c r="D2174" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="E2174" t="inlineStr">
+        <is>
+          <t>判定不能</t>
+        </is>
+      </c>
       <c r="F2174" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -69776,11 +70000,19 @@
           <t>B0F8B4CZYX</t>
         </is>
       </c>
-      <c r="D2175" t="inlineStr"/>
-      <c r="E2175" t="inlineStr"/>
+      <c r="D2175" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2175" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -69800,11 +70032,19 @@
           <t>B0F8B4KMPD</t>
         </is>
       </c>
-      <c r="D2176" t="inlineStr"/>
-      <c r="E2176" t="inlineStr"/>
+      <c r="D2176" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2176" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -69824,11 +70064,19 @@
           <t>B0F8B623PB</t>
         </is>
       </c>
-      <c r="D2177" t="inlineStr"/>
-      <c r="E2177" t="inlineStr"/>
+      <c r="D2177" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2177" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -69848,11 +70096,19 @@
           <t>B0F8B7FNDJ</t>
         </is>
       </c>
-      <c r="D2178" t="inlineStr"/>
-      <c r="E2178" t="inlineStr"/>
+      <c r="D2178" t="inlineStr">
+        <is>
+          <t>IPASON</t>
+        </is>
+      </c>
+      <c r="E2178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2178" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -69872,11 +70128,19 @@
           <t>B0F8BHMZ51</t>
         </is>
       </c>
-      <c r="D2179" t="inlineStr"/>
-      <c r="E2179" t="inlineStr"/>
+      <c r="D2179" t="inlineStr">
+        <is>
+          <t>Topsand</t>
+        </is>
+      </c>
+      <c r="E2179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2179" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -69896,11 +70160,19 @@
           <t>B0F8GG6PP7</t>
         </is>
       </c>
-      <c r="D2180" t="inlineStr"/>
-      <c r="E2180" t="inlineStr"/>
+      <c r="D2180" t="inlineStr">
+        <is>
+          <t>バンダイナムコフィルムワークス (出演) 形式: DVD</t>
+        </is>
+      </c>
+      <c r="E2180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2180" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -69920,11 +70192,19 @@
           <t>B0F8HPF4JQ</t>
         </is>
       </c>
-      <c r="D2181" t="inlineStr"/>
-      <c r="E2181" t="inlineStr"/>
+      <c r="D2181" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="E2181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2181" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -69944,11 +70224,19 @@
           <t>B0F8HVDQFT</t>
         </is>
       </c>
-      <c r="D2182" t="inlineStr"/>
-      <c r="E2182" t="inlineStr"/>
+      <c r="D2182" t="inlineStr">
+        <is>
+          <t>ONE OK ROCK (アーティスト, 演奏, 作曲) 形式: LP Record</t>
+        </is>
+      </c>
+      <c r="E2182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2182" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -69968,11 +70256,19 @@
           <t>B0F8J5HW21</t>
         </is>
       </c>
-      <c r="D2183" t="inlineStr"/>
-      <c r="E2183" t="inlineStr"/>
+      <c r="D2183" t="inlineStr">
+        <is>
+          <t>SUNFOUNDER</t>
+        </is>
+      </c>
+      <c r="E2183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2183" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -69992,11 +70288,19 @@
           <t>B0F98D8TXF</t>
         </is>
       </c>
-      <c r="D2184" t="inlineStr"/>
-      <c r="E2184" t="inlineStr"/>
+      <c r="D2184" t="inlineStr">
+        <is>
+          <t>ソイ・チェン (監督), ルイス・クー (出演), レイモンド・ラム (出演) 形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2184" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70016,11 +70320,19 @@
           <t>B0F98KKJTD</t>
         </is>
       </c>
-      <c r="D2185" t="inlineStr"/>
-      <c r="E2185" t="inlineStr"/>
+      <c r="D2185" t="inlineStr">
+        <is>
+          <t>ソイ・チェン (監督), ルイス・クー (出演), レイモンド・ラム (出演) 形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2185" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70040,11 +70352,19 @@
           <t>B0F98KQL5J</t>
         </is>
       </c>
-      <c r="D2186" t="inlineStr"/>
-      <c r="E2186" t="inlineStr"/>
+      <c r="D2186" t="inlineStr">
+        <is>
+          <t>ソイ・チェン (監督), ルイス・クー (出演), レイモンド・ラム (出演) 形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2186" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70064,11 +70384,19 @@
           <t>B0F98KSYQQ</t>
         </is>
       </c>
-      <c r="D2187" t="inlineStr"/>
-      <c r="E2187" t="inlineStr"/>
+      <c r="D2187" t="inlineStr">
+        <is>
+          <t>ソイ・チェン (監督), ルイス・クー (出演), レイモンド・ラム (出演) 形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2187" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70088,11 +70416,19 @@
           <t>B0F992NHK9</t>
         </is>
       </c>
-      <c r="D2188" t="inlineStr"/>
-      <c r="E2188" t="inlineStr"/>
+      <c r="D2188" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2188" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70112,11 +70448,19 @@
           <t>B0F99BW1H4</t>
         </is>
       </c>
-      <c r="D2189" t="inlineStr"/>
-      <c r="E2189" t="inlineStr"/>
+      <c r="D2189" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2189" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70136,11 +70480,19 @@
           <t>B0F99H6MDC</t>
         </is>
       </c>
-      <c r="D2190" t="inlineStr"/>
-      <c r="E2190" t="inlineStr"/>
+      <c r="D2190" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2190" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70160,11 +70512,19 @@
           <t>B0F99PHPRC</t>
         </is>
       </c>
-      <c r="D2191" t="inlineStr"/>
-      <c r="E2191" t="inlineStr"/>
+      <c r="D2191" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2191" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70184,11 +70544,19 @@
           <t>B0F99ZSG1N</t>
         </is>
       </c>
-      <c r="D2192" t="inlineStr"/>
-      <c r="E2192" t="inlineStr"/>
+      <c r="D2192" t="inlineStr">
+        <is>
+          <t>オアシス 形式: CD</t>
+        </is>
+      </c>
+      <c r="E2192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2192" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70208,11 +70576,19 @@
           <t>B0F9B16ZL4</t>
         </is>
       </c>
-      <c r="D2193" t="inlineStr"/>
-      <c r="E2193" t="inlineStr"/>
+      <c r="D2193" t="inlineStr">
+        <is>
+          <t>オアシス 形式: LP Record</t>
+        </is>
+      </c>
+      <c r="E2193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2193" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70232,11 +70608,19 @@
           <t>B0F9B21ZF2</t>
         </is>
       </c>
-      <c r="D2194" t="inlineStr"/>
-      <c r="E2194" t="inlineStr"/>
+      <c r="D2194" t="inlineStr">
+        <is>
+          <t>Oasis (アーティスト), - (演奏, 作曲) 形式: CD</t>
+        </is>
+      </c>
+      <c r="E2194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2194" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70256,11 +70640,19 @@
           <t>B0F9B3P4ZF</t>
         </is>
       </c>
-      <c r="D2195" t="inlineStr"/>
-      <c r="E2195" t="inlineStr"/>
+      <c r="D2195" t="inlineStr">
+        <is>
+          <t>THE FLIGHT &amp; TEKE::TEKE &amp; THUNDERDRUM FEAT. TIGGS DA AUTHOR (アーティスト) 形式: LP Record</t>
+        </is>
+      </c>
+      <c r="E2195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2195" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70280,11 +70672,19 @@
           <t>B0F9BDLRFY</t>
         </is>
       </c>
-      <c r="D2196" t="inlineStr"/>
-      <c r="E2196" t="inlineStr"/>
+      <c r="D2196" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="E2196" t="inlineStr">
+        <is>
+          <t>判定不能</t>
+        </is>
+      </c>
       <c r="F2196" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70304,11 +70704,19 @@
           <t>B0F9BJKFVX</t>
         </is>
       </c>
-      <c r="D2197" t="inlineStr"/>
-      <c r="E2197" t="inlineStr"/>
+      <c r="D2197" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="E2197" t="inlineStr">
+        <is>
+          <t>判定不能</t>
+        </is>
+      </c>
       <c r="F2197" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70328,11 +70736,19 @@
           <t>B0F9DDYCW5</t>
         </is>
       </c>
-      <c r="D2198" t="inlineStr"/>
-      <c r="E2198" t="inlineStr"/>
+      <c r="D2198" t="inlineStr">
+        <is>
+          <t>パブロ・ベルヘル (出演) 形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2198" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70352,11 +70768,19 @@
           <t>B0F9DXVSGT</t>
         </is>
       </c>
-      <c r="D2199" t="inlineStr"/>
-      <c r="E2199" t="inlineStr"/>
+      <c r="D2199" t="inlineStr">
+        <is>
+          <t>パブロ・ベルヘル (出演) 形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2199" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70376,11 +70800,19 @@
           <t>B0F9FGYMCQ</t>
         </is>
       </c>
-      <c r="D2200" t="inlineStr"/>
-      <c r="E2200" t="inlineStr"/>
+      <c r="D2200" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2200" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70400,11 +70832,19 @@
           <t>B0F9FHN69M</t>
         </is>
       </c>
-      <c r="D2201" t="inlineStr"/>
-      <c r="E2201" t="inlineStr"/>
+      <c r="D2201" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2201" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70424,11 +70864,19 @@
           <t>B0F9FJD8JD</t>
         </is>
       </c>
-      <c r="D2202" t="inlineStr"/>
-      <c r="E2202" t="inlineStr"/>
+      <c r="D2202" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2202" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70448,11 +70896,19 @@
           <t>B0F9NM1GZJ</t>
         </is>
       </c>
-      <c r="D2203" t="inlineStr"/>
-      <c r="E2203" t="inlineStr"/>
+      <c r="D2203" t="inlineStr">
+        <is>
+          <t>BekoQurd</t>
+        </is>
+      </c>
+      <c r="E2203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2203" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -70472,11 +70928,19 @@
           <t>B0F9NMBY76</t>
         </is>
       </c>
-      <c r="D2204" t="inlineStr"/>
-      <c r="E2204" t="inlineStr"/>
+      <c r="D2204" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2204" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70496,11 +70960,19 @@
           <t>B0F9NMXNFN</t>
         </is>
       </c>
-      <c r="D2205" t="inlineStr"/>
-      <c r="E2205" t="inlineStr"/>
+      <c r="D2205" t="inlineStr">
+        <is>
+          <t>Biwin</t>
+        </is>
+      </c>
+      <c r="E2205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2205" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -70520,11 +70992,19 @@
           <t>B0F9NS8VWT</t>
         </is>
       </c>
-      <c r="D2206" t="inlineStr"/>
-      <c r="E2206" t="inlineStr"/>
+      <c r="D2206" t="inlineStr">
+        <is>
+          <t>Biwin</t>
+        </is>
+      </c>
+      <c r="E2206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2206" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -70544,11 +71024,19 @@
           <t>B0F9PFDXCS</t>
         </is>
       </c>
-      <c r="D2207" t="inlineStr"/>
-      <c r="E2207" t="inlineStr"/>
+      <c r="D2207" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2207" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70568,11 +71056,19 @@
           <t>B0F9PK1CLS</t>
         </is>
       </c>
-      <c r="D2208" t="inlineStr"/>
-      <c r="E2208" t="inlineStr"/>
+      <c r="D2208" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2208" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70592,11 +71088,19 @@
           <t>B0F9TM5VXF</t>
         </is>
       </c>
-      <c r="D2209" t="inlineStr"/>
-      <c r="E2209" t="inlineStr"/>
+      <c r="D2209" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2209" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70616,11 +71120,19 @@
           <t>B0F9VHDWJ2</t>
         </is>
       </c>
-      <c r="D2210" t="inlineStr"/>
-      <c r="E2210" t="inlineStr"/>
+      <c r="D2210" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2210" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70640,11 +71152,19 @@
           <t>B0F9WSMM4P</t>
         </is>
       </c>
-      <c r="D2211" t="inlineStr"/>
-      <c r="E2211" t="inlineStr"/>
+      <c r="D2211" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2211" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70664,11 +71184,19 @@
           <t>B0F9WSWM6M</t>
         </is>
       </c>
-      <c r="D2212" t="inlineStr"/>
-      <c r="E2212" t="inlineStr"/>
+      <c r="D2212" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2212" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70688,11 +71216,19 @@
           <t>B0F9WTDRHD</t>
         </is>
       </c>
-      <c r="D2213" t="inlineStr"/>
-      <c r="E2213" t="inlineStr"/>
+      <c r="D2213" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2213" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70712,11 +71248,19 @@
           <t>B0F9XFBXJD</t>
         </is>
       </c>
-      <c r="D2214" t="inlineStr"/>
-      <c r="E2214" t="inlineStr"/>
+      <c r="D2214" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2214" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70736,11 +71280,19 @@
           <t>B0F9XFK389</t>
         </is>
       </c>
-      <c r="D2215" t="inlineStr"/>
-      <c r="E2215" t="inlineStr"/>
+      <c r="D2215" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2215" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70760,11 +71312,19 @@
           <t>B0F9XFL58J</t>
         </is>
       </c>
-      <c r="D2216" t="inlineStr"/>
-      <c r="E2216" t="inlineStr"/>
+      <c r="D2216" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2216" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70784,11 +71344,19 @@
           <t>B0F9XFN1RS</t>
         </is>
       </c>
-      <c r="D2217" t="inlineStr"/>
-      <c r="E2217" t="inlineStr"/>
+      <c r="D2217" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2217" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70808,11 +71376,19 @@
           <t>B0F9XFSVHD</t>
         </is>
       </c>
-      <c r="D2218" t="inlineStr"/>
-      <c r="E2218" t="inlineStr"/>
+      <c r="D2218" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2218" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70832,11 +71408,19 @@
           <t>B0F9XG2FDP</t>
         </is>
       </c>
-      <c r="D2219" t="inlineStr"/>
-      <c r="E2219" t="inlineStr"/>
+      <c r="D2219" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2219" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70856,11 +71440,19 @@
           <t>B0F9XG8XMX</t>
         </is>
       </c>
-      <c r="D2220" t="inlineStr"/>
-      <c r="E2220" t="inlineStr"/>
+      <c r="D2220" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2220" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70880,11 +71472,19 @@
           <t>B0F9XH5HS7</t>
         </is>
       </c>
-      <c r="D2221" t="inlineStr"/>
-      <c r="E2221" t="inlineStr"/>
+      <c r="D2221" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2221" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70904,11 +71504,19 @@
           <t>B0FB3NZDTJ</t>
         </is>
       </c>
-      <c r="D2222" t="inlineStr"/>
-      <c r="E2222" t="inlineStr"/>
+      <c r="D2222" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2222" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70928,11 +71536,19 @@
           <t>B0FB3PT8G1</t>
         </is>
       </c>
-      <c r="D2223" t="inlineStr"/>
-      <c r="E2223" t="inlineStr"/>
+      <c r="D2223" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2223" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70952,11 +71568,19 @@
           <t>B0FB3Q48SG</t>
         </is>
       </c>
-      <c r="D2224" t="inlineStr"/>
-      <c r="E2224" t="inlineStr"/>
+      <c r="D2224" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2224" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -70976,11 +71600,19 @@
           <t>B0FB3TYQJH</t>
         </is>
       </c>
-      <c r="D2225" t="inlineStr"/>
-      <c r="E2225" t="inlineStr"/>
+      <c r="D2225" t="inlineStr">
+        <is>
+          <t>TEWENE</t>
+        </is>
+      </c>
+      <c r="E2225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2225" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -71000,11 +71632,19 @@
           <t>B0FB3VYZDR</t>
         </is>
       </c>
-      <c r="D2226" t="inlineStr"/>
-      <c r="E2226" t="inlineStr"/>
+      <c r="D2226" t="inlineStr">
+        <is>
+          <t>Bmax</t>
+        </is>
+      </c>
+      <c r="E2226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2226" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -71024,11 +71664,19 @@
           <t>B0FBFMRJ2H</t>
         </is>
       </c>
-      <c r="D2227" t="inlineStr"/>
-      <c r="E2227" t="inlineStr"/>
+      <c r="D2227" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2227" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -71048,11 +71696,19 @@
           <t>B0FBFTD18V</t>
         </is>
       </c>
-      <c r="D2228" t="inlineStr"/>
-      <c r="E2228" t="inlineStr"/>
+      <c r="D2228" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2228" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -71072,11 +71728,19 @@
           <t>B0FBG57YK4</t>
         </is>
       </c>
-      <c r="D2229" t="inlineStr"/>
-      <c r="E2229" t="inlineStr"/>
+      <c r="D2229" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2229" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -71096,11 +71760,19 @@
           <t>B0FBG5BXDB</t>
         </is>
       </c>
-      <c r="D2230" t="inlineStr"/>
-      <c r="E2230" t="inlineStr"/>
+      <c r="D2230" t="inlineStr">
+        <is>
+          <t>BINHENGLON</t>
+        </is>
+      </c>
+      <c r="E2230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2230" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -71120,11 +71792,19 @@
           <t>B0FBG96MNJ</t>
         </is>
       </c>
-      <c r="D2231" t="inlineStr"/>
-      <c r="E2231" t="inlineStr"/>
+      <c r="D2231" t="inlineStr">
+        <is>
+          <t>MyDual</t>
+        </is>
+      </c>
+      <c r="E2231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2231" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -71144,11 +71824,19 @@
           <t>B0FBG9KTH4</t>
         </is>
       </c>
-      <c r="D2232" t="inlineStr"/>
-      <c r="E2232" t="inlineStr"/>
+      <c r="D2232" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2232" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -71168,11 +71856,19 @@
           <t>B0FBGNLBWK</t>
         </is>
       </c>
-      <c r="D2233" t="inlineStr"/>
-      <c r="E2233" t="inlineStr"/>
+      <c r="D2233" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2233" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -71192,11 +71888,19 @@
           <t>B0FBKTKQR9</t>
         </is>
       </c>
-      <c r="D2234" t="inlineStr"/>
-      <c r="E2234" t="inlineStr"/>
+      <c r="D2234" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2234" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -71216,11 +71920,19 @@
           <t>B0FBKWCM6W</t>
         </is>
       </c>
-      <c r="D2235" t="inlineStr"/>
-      <c r="E2235" t="inlineStr"/>
+      <c r="D2235" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2235" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -71240,11 +71952,19 @@
           <t>B0FBKXMCMS</t>
         </is>
       </c>
-      <c r="D2236" t="inlineStr"/>
-      <c r="E2236" t="inlineStr"/>
+      <c r="D2236" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2236" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -71264,11 +71984,19 @@
           <t>B0FBMDCZLK</t>
         </is>
       </c>
-      <c r="D2237" t="inlineStr"/>
-      <c r="E2237" t="inlineStr"/>
+      <c r="D2237" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="E2237" t="inlineStr">
+        <is>
+          <t>判定不能</t>
+        </is>
+      </c>
       <c r="F2237" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -71288,11 +72016,19 @@
           <t>B0FBRGNVYT</t>
         </is>
       </c>
-      <c r="D2238" t="inlineStr"/>
-      <c r="E2238" t="inlineStr"/>
+      <c r="D2238" t="inlineStr">
+        <is>
+          <t>桂馬一 (監督) 形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2238" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -71312,11 +72048,19 @@
           <t>B0FBRNL5F5</t>
         </is>
       </c>
-      <c r="D2239" t="inlineStr"/>
-      <c r="E2239" t="inlineStr"/>
+      <c r="D2239" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="E2239" t="inlineStr">
+        <is>
+          <t>判定不能</t>
+        </is>
+      </c>
       <c r="F2239" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -71336,11 +72080,19 @@
           <t>B0FBW9SB1Q</t>
         </is>
       </c>
-      <c r="D2240" t="inlineStr"/>
-      <c r="E2240" t="inlineStr"/>
+      <c r="D2240" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2240" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -71360,11 +72112,19 @@
           <t>B0FBWM6WFJ</t>
         </is>
       </c>
-      <c r="D2241" t="inlineStr"/>
-      <c r="E2241" t="inlineStr"/>
+      <c r="D2241" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2241" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -71384,11 +72144,19 @@
           <t>B0FBWX7P85</t>
         </is>
       </c>
-      <c r="D2242" t="inlineStr"/>
-      <c r="E2242" t="inlineStr"/>
+      <c r="D2242" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2242" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -71408,11 +72176,19 @@
           <t>B0FBWX8SKJ</t>
         </is>
       </c>
-      <c r="D2243" t="inlineStr"/>
-      <c r="E2243" t="inlineStr"/>
+      <c r="D2243" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2243" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -71432,11 +72208,19 @@
           <t>B0FC2YCV42</t>
         </is>
       </c>
-      <c r="D2244" t="inlineStr"/>
-      <c r="E2244" t="inlineStr"/>
+      <c r="D2244" t="inlineStr">
+        <is>
+          <t>The Beatles (アーティスト) 形式: CD</t>
+        </is>
+      </c>
+      <c r="E2244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2244" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -71456,11 +72240,19 @@
           <t>B0FC34NNM1</t>
         </is>
       </c>
-      <c r="D2245" t="inlineStr"/>
-      <c r="E2245" t="inlineStr"/>
+      <c r="D2245" t="inlineStr">
+        <is>
+          <t>キース・ジャレット ゲイリー・ピーコック 形式: LP Record</t>
+        </is>
+      </c>
+      <c r="E2245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2245" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -71480,11 +72272,19 @@
           <t>B0FC6Z84M2</t>
         </is>
       </c>
-      <c r="D2246" t="inlineStr"/>
-      <c r="E2246" t="inlineStr"/>
+      <c r="D2246" t="inlineStr">
+        <is>
+          <t>The Beatles (アーティスト) 形式: LP Record</t>
+        </is>
+      </c>
+      <c r="E2246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2246" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -71504,11 +72304,19 @@
           <t>B0FCHZ55LQ</t>
         </is>
       </c>
-      <c r="D2247" t="inlineStr"/>
-      <c r="E2247" t="inlineStr"/>
+      <c r="D2247" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="E2247" t="inlineStr">
+        <is>
+          <t>判定不能</t>
+        </is>
+      </c>
       <c r="F2247" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -71528,11 +72336,19 @@
           <t>B0FCLCN6DQ</t>
         </is>
       </c>
-      <c r="D2248" t="inlineStr"/>
-      <c r="E2248" t="inlineStr"/>
+      <c r="D2248" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2248" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -71552,11 +72368,19 @@
           <t>B0FCLKHHDG</t>
         </is>
       </c>
-      <c r="D2249" t="inlineStr"/>
-      <c r="E2249" t="inlineStr"/>
+      <c r="D2249" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2249" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -71576,11 +72400,19 @@
           <t>B0FCRP87PP</t>
         </is>
       </c>
-      <c r="D2250" t="inlineStr"/>
-      <c r="E2250" t="inlineStr"/>
+      <c r="D2250" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2250" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -71600,11 +72432,19 @@
           <t>B0FCYT6VCK</t>
         </is>
       </c>
-      <c r="D2251" t="inlineStr"/>
-      <c r="E2251" t="inlineStr"/>
+      <c r="D2251" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2251" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -71624,11 +72464,19 @@
           <t>B0FCYTWKCG</t>
         </is>
       </c>
-      <c r="D2252" t="inlineStr"/>
-      <c r="E2252" t="inlineStr"/>
+      <c r="D2252" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2252" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -71648,11 +72496,19 @@
           <t>B0FCYWHDRD</t>
         </is>
       </c>
-      <c r="D2253" t="inlineStr"/>
-      <c r="E2253" t="inlineStr"/>
+      <c r="D2253" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2253" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -71672,11 +72528,19 @@
           <t>B0FCYWM5GY</t>
         </is>
       </c>
-      <c r="D2254" t="inlineStr"/>
-      <c r="E2254" t="inlineStr"/>
+      <c r="D2254" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2254" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -71696,11 +72560,19 @@
           <t>B0FD3DQ93R</t>
         </is>
       </c>
-      <c r="D2255" t="inlineStr"/>
-      <c r="E2255" t="inlineStr"/>
+      <c r="D2255" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2255" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -71720,11 +72592,19 @@
           <t>B0FD3LTXLX</t>
         </is>
       </c>
-      <c r="D2256" t="inlineStr"/>
-      <c r="E2256" t="inlineStr"/>
+      <c r="D2256" t="inlineStr">
+        <is>
+          <t>GravaStar</t>
+        </is>
+      </c>
+      <c r="E2256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2256" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -71744,11 +72624,19 @@
           <t>B0FD3MJ8HN</t>
         </is>
       </c>
-      <c r="D2257" t="inlineStr"/>
-      <c r="E2257" t="inlineStr"/>
+      <c r="D2257" t="inlineStr">
+        <is>
+          <t>形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2257" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -71768,11 +72656,19 @@
           <t>B0FD3N1GY7</t>
         </is>
       </c>
-      <c r="D2258" t="inlineStr"/>
-      <c r="E2258" t="inlineStr"/>
+      <c r="D2258" t="inlineStr">
+        <is>
+          <t>形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2258" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -71792,11 +72688,19 @@
           <t>B0FD3PS94L</t>
         </is>
       </c>
-      <c r="D2259" t="inlineStr"/>
-      <c r="E2259" t="inlineStr"/>
+      <c r="D2259" t="inlineStr">
+        <is>
+          <t>形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2259" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -71816,11 +72720,19 @@
           <t>B0FD3QGSK6</t>
         </is>
       </c>
-      <c r="D2260" t="inlineStr"/>
-      <c r="E2260" t="inlineStr"/>
+      <c r="D2260" t="inlineStr">
+        <is>
+          <t>形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2260" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -71840,11 +72752,19 @@
           <t>B0FD6S5FPF</t>
         </is>
       </c>
-      <c r="D2261" t="inlineStr"/>
-      <c r="E2261" t="inlineStr"/>
+      <c r="D2261" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2261" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -71864,11 +72784,19 @@
           <t>B0FD8J5653</t>
         </is>
       </c>
-      <c r="D2262" t="inlineStr"/>
-      <c r="E2262" t="inlineStr"/>
+      <c r="D2262" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2262" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -71888,11 +72816,19 @@
           <t>B0FD8KV4R1</t>
         </is>
       </c>
-      <c r="D2263" t="inlineStr"/>
-      <c r="E2263" t="inlineStr"/>
+      <c r="D2263" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2263" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -71912,11 +72848,19 @@
           <t>B0FD8L2W3G</t>
         </is>
       </c>
-      <c r="D2264" t="inlineStr"/>
-      <c r="E2264" t="inlineStr"/>
+      <c r="D2264" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2264" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -71936,11 +72880,19 @@
           <t>B0FD8SDVNV</t>
         </is>
       </c>
-      <c r="D2265" t="inlineStr"/>
-      <c r="E2265" t="inlineStr"/>
+      <c r="D2265" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2265" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -71960,11 +72912,19 @@
           <t>B0FD8T19ZP</t>
         </is>
       </c>
-      <c r="D2266" t="inlineStr"/>
-      <c r="E2266" t="inlineStr"/>
+      <c r="D2266" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2266" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -71984,11 +72944,19 @@
           <t>B0FD8TJYGP</t>
         </is>
       </c>
-      <c r="D2267" t="inlineStr"/>
-      <c r="E2267" t="inlineStr"/>
+      <c r="D2267" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2267" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72008,11 +72976,19 @@
           <t>B0FD973FB1</t>
         </is>
       </c>
-      <c r="D2268" t="inlineStr"/>
-      <c r="E2268" t="inlineStr"/>
+      <c r="D2268" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2268" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72032,11 +73008,19 @@
           <t>B0FD99JJGK</t>
         </is>
       </c>
-      <c r="D2269" t="inlineStr"/>
-      <c r="E2269" t="inlineStr"/>
+      <c r="D2269" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2269" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72056,11 +73040,19 @@
           <t>B0FD99NW15</t>
         </is>
       </c>
-      <c r="D2270" t="inlineStr"/>
-      <c r="E2270" t="inlineStr"/>
+      <c r="D2270" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2270" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72080,11 +73072,19 @@
           <t>B0FD9FMTS8</t>
         </is>
       </c>
-      <c r="D2271" t="inlineStr"/>
-      <c r="E2271" t="inlineStr"/>
+      <c r="D2271" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2271" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72104,11 +73104,19 @@
           <t>B0FD9GNFTS</t>
         </is>
       </c>
-      <c r="D2272" t="inlineStr"/>
-      <c r="E2272" t="inlineStr"/>
+      <c r="D2272" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2272" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72128,11 +73136,19 @@
           <t>B0FD9M7M75</t>
         </is>
       </c>
-      <c r="D2273" t="inlineStr"/>
-      <c r="E2273" t="inlineStr"/>
+      <c r="D2273" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2273" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72152,11 +73168,19 @@
           <t>B0FD9WZDQD</t>
         </is>
       </c>
-      <c r="D2274" t="inlineStr"/>
-      <c r="E2274" t="inlineStr"/>
+      <c r="D2274" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2274" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72176,11 +73200,19 @@
           <t>B0FDB6KFKR</t>
         </is>
       </c>
-      <c r="D2275" t="inlineStr"/>
-      <c r="E2275" t="inlineStr"/>
+      <c r="D2275" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2275" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72200,11 +73232,19 @@
           <t>B0FDFVVD4C</t>
         </is>
       </c>
-      <c r="D2276" t="inlineStr"/>
-      <c r="E2276" t="inlineStr"/>
+      <c r="D2276" t="inlineStr">
+        <is>
+          <t>古賀一臣 (監督) 形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2276" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72224,11 +73264,19 @@
           <t>B0FDFW1QTS</t>
         </is>
       </c>
-      <c r="D2277" t="inlineStr"/>
-      <c r="E2277" t="inlineStr"/>
+      <c r="D2277" t="inlineStr">
+        <is>
+          <t>古賀一臣 (監督) 形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2277" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72248,11 +73296,19 @@
           <t>B0FDFW3P12</t>
         </is>
       </c>
-      <c r="D2278" t="inlineStr"/>
-      <c r="E2278" t="inlineStr"/>
+      <c r="D2278" t="inlineStr">
+        <is>
+          <t>古賀一臣 (監督) 形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2278" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72272,11 +73328,19 @@
           <t>B0FDFZBGXF</t>
         </is>
       </c>
-      <c r="D2279" t="inlineStr"/>
-      <c r="E2279" t="inlineStr"/>
+      <c r="D2279" t="inlineStr">
+        <is>
+          <t>古賀一臣 (監督) 形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2279" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72296,11 +73360,19 @@
           <t>B0FDH8KHKH</t>
         </is>
       </c>
-      <c r="D2280" t="inlineStr"/>
-      <c r="E2280" t="inlineStr"/>
+      <c r="D2280" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="E2280" t="inlineStr">
+        <is>
+          <t>判定不能</t>
+        </is>
+      </c>
       <c r="F2280" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72320,11 +73392,19 @@
           <t>B0FDJYP97B</t>
         </is>
       </c>
-      <c r="D2281" t="inlineStr"/>
-      <c r="E2281" t="inlineStr"/>
+      <c r="D2281" t="inlineStr">
+        <is>
+          <t>suevery</t>
+        </is>
+      </c>
+      <c r="E2281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2281" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -72344,11 +73424,19 @@
           <t>B0FDKLGX8R</t>
         </is>
       </c>
-      <c r="D2282" t="inlineStr"/>
-      <c r="E2282" t="inlineStr"/>
+      <c r="D2282" t="inlineStr">
+        <is>
+          <t>ポルノグラフィティ (出演) 形式: DVD</t>
+        </is>
+      </c>
+      <c r="E2282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2282" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72368,11 +73456,19 @@
           <t>B0FDKM8MHH</t>
         </is>
       </c>
-      <c r="D2283" t="inlineStr"/>
-      <c r="E2283" t="inlineStr"/>
+      <c r="D2283" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2283" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72392,11 +73488,19 @@
           <t>B0FDKNMSSX</t>
         </is>
       </c>
-      <c r="D2284" t="inlineStr"/>
-      <c r="E2284" t="inlineStr"/>
+      <c r="D2284" t="inlineStr">
+        <is>
+          <t>ポルノグラフィティ (出演) 形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2284" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72416,11 +73520,19 @@
           <t>B0FDKPF16F</t>
         </is>
       </c>
-      <c r="D2285" t="inlineStr"/>
-      <c r="E2285" t="inlineStr"/>
+      <c r="D2285" t="inlineStr">
+        <is>
+          <t>ポルノグラフィティ (出演) 形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2285" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72440,11 +73552,19 @@
           <t>B0FDKPVD4D</t>
         </is>
       </c>
-      <c r="D2286" t="inlineStr"/>
-      <c r="E2286" t="inlineStr"/>
+      <c r="D2286" t="inlineStr">
+        <is>
+          <t>ポルノグラフィティ (出演) 形式: DVD</t>
+        </is>
+      </c>
+      <c r="E2286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2286" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72464,11 +73584,19 @@
           <t>B0FDKRXTMC</t>
         </is>
       </c>
-      <c r="D2287" t="inlineStr"/>
-      <c r="E2287" t="inlineStr"/>
+      <c r="D2287" t="inlineStr">
+        <is>
+          <t>ポルノグラフィティ (出演) 形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2287" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72488,11 +73616,19 @@
           <t>B0FDKTLYTG</t>
         </is>
       </c>
-      <c r="D2288" t="inlineStr"/>
-      <c r="E2288" t="inlineStr"/>
+      <c r="D2288" t="inlineStr">
+        <is>
+          <t>BE:FIRST (出演) 形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2288" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72512,11 +73648,19 @@
           <t>B0FDKW6TRY</t>
         </is>
       </c>
-      <c r="D2289" t="inlineStr"/>
-      <c r="E2289" t="inlineStr"/>
+      <c r="D2289" t="inlineStr">
+        <is>
+          <t>BE:FIRST (出演) 形式: DVD</t>
+        </is>
+      </c>
+      <c r="E2289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2289" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72536,11 +73680,19 @@
           <t>B0FDL2VQCH</t>
         </is>
       </c>
-      <c r="D2290" t="inlineStr"/>
-      <c r="E2290" t="inlineStr"/>
+      <c r="D2290" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2290" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72560,11 +73712,19 @@
           <t>B0FDL42R9Y</t>
         </is>
       </c>
-      <c r="D2291" t="inlineStr"/>
-      <c r="E2291" t="inlineStr"/>
+      <c r="D2291" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2291" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72584,11 +73744,19 @@
           <t>B0FDL4QV97</t>
         </is>
       </c>
-      <c r="D2292" t="inlineStr"/>
-      <c r="E2292" t="inlineStr"/>
+      <c r="D2292" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2292" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72608,11 +73776,19 @@
           <t>B0FDL51M9F</t>
         </is>
       </c>
-      <c r="D2293" t="inlineStr"/>
-      <c r="E2293" t="inlineStr"/>
+      <c r="D2293" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2293" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72632,11 +73808,19 @@
           <t>B0FDL6WMKF</t>
         </is>
       </c>
-      <c r="D2294" t="inlineStr"/>
-      <c r="E2294" t="inlineStr"/>
+      <c r="D2294" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2294" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72656,11 +73840,19 @@
           <t>B0FDL75N23</t>
         </is>
       </c>
-      <c r="D2295" t="inlineStr"/>
-      <c r="E2295" t="inlineStr"/>
+      <c r="D2295" t="inlineStr">
+        <is>
+          <t>Chrome 形式: LP Record</t>
+        </is>
+      </c>
+      <c r="E2295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2295" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72680,11 +73872,19 @@
           <t>B0FDLQLKSW</t>
         </is>
       </c>
-      <c r="D2296" t="inlineStr"/>
-      <c r="E2296" t="inlineStr"/>
+      <c r="D2296" t="inlineStr">
+        <is>
+          <t>Susumu Yokota (アーティスト) 形式: CD</t>
+        </is>
+      </c>
+      <c r="E2296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2296" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72704,11 +73904,19 @@
           <t>B0FDP738L9</t>
         </is>
       </c>
-      <c r="D2297" t="inlineStr"/>
-      <c r="E2297" t="inlineStr"/>
+      <c r="D2297" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2297" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72728,11 +73936,19 @@
           <t>B0FDPJY89T</t>
         </is>
       </c>
-      <c r="D2298" t="inlineStr"/>
-      <c r="E2298" t="inlineStr"/>
+      <c r="D2298" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2298" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72752,11 +73968,19 @@
           <t>B0FDPKBPS6</t>
         </is>
       </c>
-      <c r="D2299" t="inlineStr"/>
-      <c r="E2299" t="inlineStr"/>
+      <c r="D2299" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2299" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72776,11 +74000,19 @@
           <t>B0FDPLBQLM</t>
         </is>
       </c>
-      <c r="D2300" t="inlineStr"/>
-      <c r="E2300" t="inlineStr"/>
+      <c r="D2300" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2300" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72800,11 +74032,19 @@
           <t>B0FDPNCM5T</t>
         </is>
       </c>
-      <c r="D2301" t="inlineStr"/>
-      <c r="E2301" t="inlineStr"/>
+      <c r="D2301" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2301" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72824,11 +74064,19 @@
           <t>B0FDPZ5KX5</t>
         </is>
       </c>
-      <c r="D2302" t="inlineStr"/>
-      <c r="E2302" t="inlineStr"/>
+      <c r="D2302" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2302" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72848,11 +74096,19 @@
           <t>B0FDQF26BJ</t>
         </is>
       </c>
-      <c r="D2303" t="inlineStr"/>
-      <c r="E2303" t="inlineStr"/>
+      <c r="D2303" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2303" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72872,11 +74128,19 @@
           <t>B0FDQF4P9P</t>
         </is>
       </c>
-      <c r="D2304" t="inlineStr"/>
-      <c r="E2304" t="inlineStr"/>
+      <c r="D2304" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2304" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72896,11 +74160,19 @@
           <t>B0FDQT1CR2</t>
         </is>
       </c>
-      <c r="D2305" t="inlineStr"/>
-      <c r="E2305" t="inlineStr"/>
+      <c r="D2305" t="inlineStr">
+        <is>
+          <t>Yulix</t>
+        </is>
+      </c>
+      <c r="E2305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2305" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -72920,11 +74192,19 @@
           <t>B0FDQTMWB2</t>
         </is>
       </c>
-      <c r="D2306" t="inlineStr"/>
-      <c r="E2306" t="inlineStr"/>
+      <c r="D2306" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="E2306" t="inlineStr">
+        <is>
+          <t>判定不能</t>
+        </is>
+      </c>
       <c r="F2306" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -72944,11 +74224,19 @@
           <t>B0FDQTNJ8H</t>
         </is>
       </c>
-      <c r="D2307" t="inlineStr"/>
-      <c r="E2307" t="inlineStr"/>
+      <c r="D2307" t="inlineStr">
+        <is>
+          <t>Yulix</t>
+        </is>
+      </c>
+      <c r="E2307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2307" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -72968,11 +74256,19 @@
           <t>B0FDQTQ4ZM</t>
         </is>
       </c>
-      <c r="D2308" t="inlineStr"/>
-      <c r="E2308" t="inlineStr"/>
+      <c r="D2308" t="inlineStr">
+        <is>
+          <t>Tabtop</t>
+        </is>
+      </c>
+      <c r="E2308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2308" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -72992,11 +74288,19 @@
           <t>B0FDQVPLL7</t>
         </is>
       </c>
-      <c r="D2309" t="inlineStr"/>
-      <c r="E2309" t="inlineStr"/>
+      <c r="D2309" t="inlineStr">
+        <is>
+          <t>Yulix</t>
+        </is>
+      </c>
+      <c r="E2309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2309" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -73016,11 +74320,19 @@
           <t>B0FDTLPVKB</t>
         </is>
       </c>
-      <c r="D2310" t="inlineStr"/>
-      <c r="E2310" t="inlineStr"/>
+      <c r="D2310" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2310" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -73040,11 +74352,19 @@
           <t>B0FDTSWXSL</t>
         </is>
       </c>
-      <c r="D2311" t="inlineStr"/>
-      <c r="E2311" t="inlineStr"/>
+      <c r="D2311" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2311" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -73064,11 +74384,19 @@
           <t>B0FDVG5968</t>
         </is>
       </c>
-      <c r="D2312" t="inlineStr"/>
-      <c r="E2312" t="inlineStr"/>
+      <c r="D2312" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2312" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -73088,11 +74416,19 @@
           <t>B0FDVGB4XF</t>
         </is>
       </c>
-      <c r="D2313" t="inlineStr"/>
-      <c r="E2313" t="inlineStr"/>
+      <c r="D2313" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="E2313" t="inlineStr">
+        <is>
+          <t>判定不能</t>
+        </is>
+      </c>
       <c r="F2313" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -73112,11 +74448,19 @@
           <t>B0FDVZ5DTX</t>
         </is>
       </c>
-      <c r="D2314" t="inlineStr"/>
-      <c r="E2314" t="inlineStr"/>
+      <c r="D2314" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2314" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -73136,11 +74480,19 @@
           <t>B0FDVZSTNS</t>
         </is>
       </c>
-      <c r="D2315" t="inlineStr"/>
-      <c r="E2315" t="inlineStr"/>
+      <c r="D2315" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2315" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -73160,11 +74512,19 @@
           <t>B0FDW7CT1R</t>
         </is>
       </c>
-      <c r="D2316" t="inlineStr"/>
-      <c r="E2316" t="inlineStr"/>
+      <c r="D2316" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="E2316" t="inlineStr">
+        <is>
+          <t>判定不能</t>
+        </is>
+      </c>
       <c r="F2316" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -73184,11 +74544,19 @@
           <t>B0FDWG4KWM</t>
         </is>
       </c>
-      <c r="D2317" t="inlineStr"/>
-      <c r="E2317" t="inlineStr"/>
+      <c r="D2317" t="inlineStr">
+        <is>
+          <t>ATTACK SHARK</t>
+        </is>
+      </c>
+      <c r="E2317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2317" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -73208,11 +74576,19 @@
           <t>B0FDWM68LG</t>
         </is>
       </c>
-      <c r="D2318" t="inlineStr"/>
-      <c r="E2318" t="inlineStr"/>
+      <c r="D2318" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2318" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -73232,11 +74608,19 @@
           <t>B0FDWNH35L</t>
         </is>
       </c>
-      <c r="D2319" t="inlineStr"/>
-      <c r="E2319" t="inlineStr"/>
+      <c r="D2319" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2319" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -73256,11 +74640,19 @@
           <t>B0FDWNH87J</t>
         </is>
       </c>
-      <c r="D2320" t="inlineStr"/>
-      <c r="E2320" t="inlineStr"/>
+      <c r="D2320" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2320" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -73280,11 +74672,19 @@
           <t>B0FDWNQBP2</t>
         </is>
       </c>
-      <c r="D2321" t="inlineStr"/>
-      <c r="E2321" t="inlineStr"/>
+      <c r="D2321" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2321" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -73304,11 +74704,19 @@
           <t>B0FDYGFXK6</t>
         </is>
       </c>
-      <c r="D2322" t="inlineStr"/>
-      <c r="E2322" t="inlineStr"/>
+      <c r="D2322" t="inlineStr">
+        <is>
+          <t>オアシス 形式: LP Record</t>
+        </is>
+      </c>
+      <c r="E2322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2322" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -73328,11 +74736,19 @@
           <t>B0FDZ6612M</t>
         </is>
       </c>
-      <c r="D2323" t="inlineStr"/>
-      <c r="E2323" t="inlineStr"/>
+      <c r="D2323" t="inlineStr">
+        <is>
+          <t>Oasis (アーティスト) 形式: LP Record</t>
+        </is>
+      </c>
+      <c r="E2323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2323" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -73352,11 +74768,19 @@
           <t>B0FF3BCTQD</t>
         </is>
       </c>
-      <c r="D2324" t="inlineStr"/>
-      <c r="E2324" t="inlineStr"/>
+      <c r="D2324" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2324" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -73376,11 +74800,19 @@
           <t>B0FF3BK52N</t>
         </is>
       </c>
-      <c r="D2325" t="inlineStr"/>
-      <c r="E2325" t="inlineStr"/>
+      <c r="D2325" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2325" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -73400,11 +74832,19 @@
           <t>B0FF3FLF8C</t>
         </is>
       </c>
-      <c r="D2326" t="inlineStr"/>
-      <c r="E2326" t="inlineStr"/>
+      <c r="D2326" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2326" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -73424,11 +74864,19 @@
           <t>B0FF3Z8P6J</t>
         </is>
       </c>
-      <c r="D2327" t="inlineStr"/>
-      <c r="E2327" t="inlineStr"/>
+      <c r="D2327" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2327" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -73448,11 +74896,19 @@
           <t>B0FF492VBR</t>
         </is>
       </c>
-      <c r="D2328" t="inlineStr"/>
-      <c r="E2328" t="inlineStr"/>
+      <c r="D2328" t="inlineStr">
+        <is>
+          <t>ecoco</t>
+        </is>
+      </c>
+      <c r="E2328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2328" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -73472,11 +74928,19 @@
           <t>B0FF4GSFLW</t>
         </is>
       </c>
-      <c r="D2329" t="inlineStr"/>
-      <c r="E2329" t="inlineStr"/>
+      <c r="D2329" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2329" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -73496,11 +74960,19 @@
           <t>B0FF4LMZL2</t>
         </is>
       </c>
-      <c r="D2330" t="inlineStr"/>
-      <c r="E2330" t="inlineStr"/>
+      <c r="D2330" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2330" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -73520,11 +74992,19 @@
           <t>B0FF4MZNRD</t>
         </is>
       </c>
-      <c r="D2331" t="inlineStr"/>
-      <c r="E2331" t="inlineStr"/>
+      <c r="D2331" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2331" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -73544,11 +75024,19 @@
           <t>B0FF4V6RK5</t>
         </is>
       </c>
-      <c r="D2332" t="inlineStr"/>
-      <c r="E2332" t="inlineStr"/>
+      <c r="D2332" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2332" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -73568,11 +75056,19 @@
           <t>B0FF4V9JDK</t>
         </is>
       </c>
-      <c r="D2333" t="inlineStr"/>
-      <c r="E2333" t="inlineStr"/>
+      <c r="D2333" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2333" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -73592,11 +75088,19 @@
           <t>B0FF51CWWW</t>
         </is>
       </c>
-      <c r="D2334" t="inlineStr"/>
-      <c r="E2334" t="inlineStr"/>
+      <c r="D2334" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2334" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -73616,11 +75120,19 @@
           <t>B0FF52SKN8</t>
         </is>
       </c>
-      <c r="D2335" t="inlineStr"/>
-      <c r="E2335" t="inlineStr"/>
+      <c r="D2335" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2335" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -73640,11 +75152,19 @@
           <t>B0FF9MBBDP</t>
         </is>
       </c>
-      <c r="D2336" t="inlineStr"/>
-      <c r="E2336" t="inlineStr"/>
+      <c r="D2336" t="inlineStr">
+        <is>
+          <t>OnePlus</t>
+        </is>
+      </c>
+      <c r="E2336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2336" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -73664,11 +75184,19 @@
           <t>B0FF9N92JZ</t>
         </is>
       </c>
-      <c r="D2337" t="inlineStr"/>
-      <c r="E2337" t="inlineStr"/>
+      <c r="D2337" t="inlineStr">
+        <is>
+          <t>PRITOM</t>
+        </is>
+      </c>
+      <c r="E2337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2337" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -73688,11 +75216,19 @@
           <t>B0FF9SC1MZ</t>
         </is>
       </c>
-      <c r="D2338" t="inlineStr"/>
-      <c r="E2338" t="inlineStr"/>
+      <c r="D2338" t="inlineStr">
+        <is>
+          <t>私立恵比寿中学 (出演) 形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2338" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -73712,11 +75248,19 @@
           <t>B0FFGVC5YX</t>
         </is>
       </c>
-      <c r="D2339" t="inlineStr"/>
-      <c r="E2339" t="inlineStr"/>
+      <c r="D2339" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2339" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -73736,11 +75280,19 @@
           <t>B0FFT8MZ4P</t>
         </is>
       </c>
-      <c r="D2340" t="inlineStr"/>
-      <c r="E2340" t="inlineStr"/>
+      <c r="D2340" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2340" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -73760,11 +75312,19 @@
           <t>B0FFTBC7X6</t>
         </is>
       </c>
-      <c r="D2341" t="inlineStr"/>
-      <c r="E2341" t="inlineStr"/>
+      <c r="D2341" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2341" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -73784,11 +75344,19 @@
           <t>B0FFTBD8V2</t>
         </is>
       </c>
-      <c r="D2342" t="inlineStr"/>
-      <c r="E2342" t="inlineStr"/>
+      <c r="D2342" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2342" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -73808,11 +75376,19 @@
           <t>B0FFTBHZXD</t>
         </is>
       </c>
-      <c r="D2343" t="inlineStr"/>
-      <c r="E2343" t="inlineStr"/>
+      <c r="D2343" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2343" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -73832,11 +75408,19 @@
           <t>B0FFTBLHT5</t>
         </is>
       </c>
-      <c r="D2344" t="inlineStr"/>
-      <c r="E2344" t="inlineStr"/>
+      <c r="D2344" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2344" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -73856,11 +75440,19 @@
           <t>B0FFTC6GS1</t>
         </is>
       </c>
-      <c r="D2345" t="inlineStr"/>
-      <c r="E2345" t="inlineStr"/>
+      <c r="D2345" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2345" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -73880,11 +75472,19 @@
           <t>B0FFTCH74T</t>
         </is>
       </c>
-      <c r="D2346" t="inlineStr"/>
-      <c r="E2346" t="inlineStr"/>
+      <c r="D2346" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2346" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -73904,11 +75504,19 @@
           <t>B0FFTCNKKM</t>
         </is>
       </c>
-      <c r="D2347" t="inlineStr"/>
-      <c r="E2347" t="inlineStr"/>
+      <c r="D2347" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2347" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -73928,11 +75536,19 @@
           <t>B0FFTCP7K5</t>
         </is>
       </c>
-      <c r="D2348" t="inlineStr"/>
-      <c r="E2348" t="inlineStr"/>
+      <c r="D2348" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2348" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -73952,11 +75568,19 @@
           <t>B0FFTDFNZX</t>
         </is>
       </c>
-      <c r="D2349" t="inlineStr"/>
-      <c r="E2349" t="inlineStr"/>
+      <c r="D2349" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2349" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -73976,11 +75600,19 @@
           <t>B0FFTDPLLF</t>
         </is>
       </c>
-      <c r="D2350" t="inlineStr"/>
-      <c r="E2350" t="inlineStr"/>
+      <c r="D2350" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2350" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -74000,11 +75632,19 @@
           <t>B0FFTF296Z</t>
         </is>
       </c>
-      <c r="D2351" t="inlineStr"/>
-      <c r="E2351" t="inlineStr"/>
+      <c r="D2351" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2351" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -74024,11 +75664,19 @@
           <t>B0FFTFPGR6</t>
         </is>
       </c>
-      <c r="D2352" t="inlineStr"/>
-      <c r="E2352" t="inlineStr"/>
+      <c r="D2352" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2352" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -74048,11 +75696,19 @@
           <t>B0FFTFPGSN</t>
         </is>
       </c>
-      <c r="D2353" t="inlineStr"/>
-      <c r="E2353" t="inlineStr"/>
+      <c r="D2353" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2353" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -74072,11 +75728,19 @@
           <t>B0FFTFPZWV</t>
         </is>
       </c>
-      <c r="D2354" t="inlineStr"/>
-      <c r="E2354" t="inlineStr"/>
+      <c r="D2354" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2354" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -74096,11 +75760,19 @@
           <t>B0FFTG4SVF</t>
         </is>
       </c>
-      <c r="D2355" t="inlineStr"/>
-      <c r="E2355" t="inlineStr"/>
+      <c r="D2355" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2355" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -74120,11 +75792,19 @@
           <t>B0FFZL1NK3</t>
         </is>
       </c>
-      <c r="D2356" t="inlineStr"/>
-      <c r="E2356" t="inlineStr"/>
+      <c r="D2356" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2356" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -74144,11 +75824,19 @@
           <t>B0FFZMT3QS</t>
         </is>
       </c>
-      <c r="D2357" t="inlineStr"/>
-      <c r="E2357" t="inlineStr"/>
+      <c r="D2357" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2357" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -74168,11 +75856,19 @@
           <t>B0FFZN9QKS</t>
         </is>
       </c>
-      <c r="D2358" t="inlineStr"/>
-      <c r="E2358" t="inlineStr"/>
+      <c r="D2358" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2358" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -74192,11 +75888,19 @@
           <t>B0FFZPXHYN</t>
         </is>
       </c>
-      <c r="D2359" t="inlineStr"/>
-      <c r="E2359" t="inlineStr"/>
+      <c r="D2359" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2359" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -74216,11 +75920,19 @@
           <t>B0FG2YNYYL</t>
         </is>
       </c>
-      <c r="D2360" t="inlineStr"/>
-      <c r="E2360" t="inlineStr"/>
+      <c r="D2360" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="E2360" t="inlineStr">
+        <is>
+          <t>判定不能</t>
+        </is>
+      </c>
       <c r="F2360" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -74240,11 +75952,19 @@
           <t>B0FG3CNHM8</t>
         </is>
       </c>
-      <c r="D2361" t="inlineStr"/>
-      <c r="E2361" t="inlineStr"/>
+      <c r="D2361" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2361" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -74264,11 +75984,19 @@
           <t>B0FG74GMN6</t>
         </is>
       </c>
-      <c r="D2362" t="inlineStr"/>
-      <c r="E2362" t="inlineStr"/>
+      <c r="D2362" t="inlineStr">
+        <is>
+          <t>cocopar</t>
+        </is>
+      </c>
+      <c r="E2362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2362" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -74288,11 +76016,19 @@
           <t>B0FG76GBP3</t>
         </is>
       </c>
-      <c r="D2363" t="inlineStr"/>
-      <c r="E2363" t="inlineStr"/>
+      <c r="D2363" t="inlineStr">
+        <is>
+          <t>Secretlab</t>
+        </is>
+      </c>
+      <c r="E2363" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2363" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -74312,11 +76048,19 @@
           <t>B0FG775KNZ</t>
         </is>
       </c>
-      <c r="D2364" t="inlineStr"/>
-      <c r="E2364" t="inlineStr"/>
+      <c r="D2364" t="inlineStr">
+        <is>
+          <t>Secretlab</t>
+        </is>
+      </c>
+      <c r="E2364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2364" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -74336,11 +76080,19 @@
           <t>B0FG7BRRN8</t>
         </is>
       </c>
-      <c r="D2365" t="inlineStr"/>
-      <c r="E2365" t="inlineStr"/>
+      <c r="D2365" t="inlineStr">
+        <is>
+          <t>Jolifield</t>
+        </is>
+      </c>
+      <c r="E2365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2365" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -74360,11 +76112,19 @@
           <t>B0FG7DGPZH</t>
         </is>
       </c>
-      <c r="D2366" t="inlineStr"/>
-      <c r="E2366" t="inlineStr"/>
+      <c r="D2366" t="inlineStr">
+        <is>
+          <t>Jolifield</t>
+        </is>
+      </c>
+      <c r="E2366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2366" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -74384,11 +76144,19 @@
           <t>B0FG7DQMP7</t>
         </is>
       </c>
-      <c r="D2367" t="inlineStr"/>
-      <c r="E2367" t="inlineStr"/>
+      <c r="D2367" t="inlineStr">
+        <is>
+          <t>Jolifield</t>
+        </is>
+      </c>
+      <c r="E2367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2367" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -74408,11 +76176,19 @@
           <t>B0FG7H4W49</t>
         </is>
       </c>
-      <c r="D2368" t="inlineStr"/>
-      <c r="E2368" t="inlineStr"/>
+      <c r="D2368" t="inlineStr">
+        <is>
+          <t>Heston, Charlton (出演), Russell, Kurt (出演) 形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2368" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -74432,11 +76208,19 @@
           <t>B0FG7H78QM</t>
         </is>
       </c>
-      <c r="D2369" t="inlineStr"/>
-      <c r="E2369" t="inlineStr"/>
+      <c r="D2369" t="inlineStr">
+        <is>
+          <t>シソンヌ (出演) 形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2369" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -74456,11 +76240,19 @@
           <t>B0FG7TGGLS</t>
         </is>
       </c>
-      <c r="D2370" t="inlineStr"/>
-      <c r="E2370" t="inlineStr"/>
+      <c r="D2370" t="inlineStr">
+        <is>
+          <t>稲葉浩志 (出演) 形式: DVD</t>
+        </is>
+      </c>
+      <c r="E2370" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2370" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -74480,11 +76272,19 @@
           <t>B0FG7TR6DN</t>
         </is>
       </c>
-      <c r="D2371" t="inlineStr"/>
-      <c r="E2371" t="inlineStr"/>
+      <c r="D2371" t="inlineStr">
+        <is>
+          <t>稲葉浩志 (出演) 形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2371" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2371" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -74504,11 +76304,19 @@
           <t>B0FG7WZX21</t>
         </is>
       </c>
-      <c r="D2372" t="inlineStr"/>
-      <c r="E2372" t="inlineStr"/>
+      <c r="D2372" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2372" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2372" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -74528,11 +76336,19 @@
           <t>B0FG7X37NB</t>
         </is>
       </c>
-      <c r="D2373" t="inlineStr"/>
-      <c r="E2373" t="inlineStr"/>
+      <c r="D2373" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2373" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2373" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -74552,11 +76368,19 @@
           <t>B0FG7X3WZV</t>
         </is>
       </c>
-      <c r="D2374" t="inlineStr"/>
-      <c r="E2374" t="inlineStr"/>
+      <c r="D2374" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2374" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2374" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -74576,11 +76400,19 @@
           <t>B0FG7X68JR</t>
         </is>
       </c>
-      <c r="D2375" t="inlineStr"/>
-      <c r="E2375" t="inlineStr"/>
+      <c r="D2375" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2375" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2375" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -74600,11 +76432,19 @@
           <t>B0FG7YJXWB</t>
         </is>
       </c>
-      <c r="D2376" t="inlineStr"/>
-      <c r="E2376" t="inlineStr"/>
+      <c r="D2376" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2376" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2376" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -74624,11 +76464,19 @@
           <t>B0FG7Z82N2</t>
         </is>
       </c>
-      <c r="D2377" t="inlineStr"/>
-      <c r="E2377" t="inlineStr"/>
+      <c r="D2377" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2377" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2377" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -74648,11 +76496,19 @@
           <t>B0FG81TJFY</t>
         </is>
       </c>
-      <c r="D2378" t="inlineStr"/>
-      <c r="E2378" t="inlineStr"/>
+      <c r="D2378" t="inlineStr">
+        <is>
+          <t>形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2378" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -74672,11 +76528,19 @@
           <t>B0FG8546F2</t>
         </is>
       </c>
-      <c r="D2379" t="inlineStr"/>
-      <c r="E2379" t="inlineStr"/>
+      <c r="D2379" t="inlineStr">
+        <is>
+          <t>形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2379" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2379" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -74696,11 +76560,19 @@
           <t>B0FG855R1R</t>
         </is>
       </c>
-      <c r="D2380" t="inlineStr"/>
-      <c r="E2380" t="inlineStr"/>
+      <c r="D2380" t="inlineStr">
+        <is>
+          <t>形式: DVD</t>
+        </is>
+      </c>
+      <c r="E2380" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2380" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -74720,11 +76592,19 @@
           <t>B0FG8G2GSL</t>
         </is>
       </c>
-      <c r="D2381" t="inlineStr"/>
-      <c r="E2381" t="inlineStr"/>
+      <c r="D2381" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2381" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2381" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -74744,11 +76624,19 @@
           <t>B0FG8GF73Y</t>
         </is>
       </c>
-      <c r="D2382" t="inlineStr"/>
-      <c r="E2382" t="inlineStr"/>
+      <c r="D2382" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2382" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -74768,11 +76656,19 @@
           <t>B0FG8GWFY1</t>
         </is>
       </c>
-      <c r="D2383" t="inlineStr"/>
-      <c r="E2383" t="inlineStr"/>
+      <c r="D2383" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2383" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2383" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -74792,11 +76688,19 @@
           <t>B0FG8HWJNV</t>
         </is>
       </c>
-      <c r="D2384" t="inlineStr"/>
-      <c r="E2384" t="inlineStr"/>
+      <c r="D2384" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2384" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2384" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -74816,11 +76720,19 @@
           <t>B0FG8K98GQ</t>
         </is>
       </c>
-      <c r="D2385" t="inlineStr"/>
-      <c r="E2385" t="inlineStr"/>
+      <c r="D2385" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2385" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2385" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -74840,11 +76752,19 @@
           <t>B0FGCN9S3S</t>
         </is>
       </c>
-      <c r="D2386" t="inlineStr"/>
-      <c r="E2386" t="inlineStr"/>
+      <c r="D2386" t="inlineStr">
+        <is>
+          <t>Bettdow</t>
+        </is>
+      </c>
+      <c r="E2386" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2386" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -74864,11 +76784,19 @@
           <t>B0FGDBK21H</t>
         </is>
       </c>
-      <c r="D2387" t="inlineStr"/>
-      <c r="E2387" t="inlineStr"/>
+      <c r="D2387" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2387" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -74888,11 +76816,19 @@
           <t>B0FGJ5QCG9</t>
         </is>
       </c>
-      <c r="D2388" t="inlineStr"/>
-      <c r="E2388" t="inlineStr"/>
+      <c r="D2388" t="inlineStr">
+        <is>
+          <t>ＣＡＮＤＹ　ＴＵＮＥ 形式: CD</t>
+        </is>
+      </c>
+      <c r="E2388" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2388" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -74912,11 +76848,19 @@
           <t>B0FGJM12N3</t>
         </is>
       </c>
-      <c r="D2389" t="inlineStr"/>
-      <c r="E2389" t="inlineStr"/>
+      <c r="D2389" t="inlineStr">
+        <is>
+          <t>ナジェール</t>
+        </is>
+      </c>
+      <c r="E2389" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2389" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -74936,11 +76880,19 @@
           <t>B0FGJMWRTW</t>
         </is>
       </c>
-      <c r="D2390" t="inlineStr"/>
-      <c r="E2390" t="inlineStr"/>
+      <c r="D2390" t="inlineStr">
+        <is>
+          <t>PETTENA</t>
+        </is>
+      </c>
+      <c r="E2390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2390" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -74960,11 +76912,19 @@
           <t>B0FGJWP9D5</t>
         </is>
       </c>
-      <c r="D2391" t="inlineStr"/>
-      <c r="E2391" t="inlineStr"/>
+      <c r="D2391" t="inlineStr">
+        <is>
+          <t>アリ・ボール (出演), ミシェル・モルガン (出演), ジュリアン・デュヴィヴィエ (監督) 形式: DVD</t>
+        </is>
+      </c>
+      <c r="E2391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2391" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -74984,11 +76944,19 @@
           <t>B0FGK1CCHN</t>
         </is>
       </c>
-      <c r="D2392" t="inlineStr"/>
-      <c r="E2392" t="inlineStr"/>
+      <c r="D2392" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2392" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75008,11 +76976,19 @@
           <t>B0FGK1ZJVS</t>
         </is>
       </c>
-      <c r="D2393" t="inlineStr"/>
-      <c r="E2393" t="inlineStr"/>
+      <c r="D2393" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2393" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75032,11 +77008,19 @@
           <t>B0FGK21HRP</t>
         </is>
       </c>
-      <c r="D2394" t="inlineStr"/>
-      <c r="E2394" t="inlineStr"/>
+      <c r="D2394" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2394" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75056,11 +77040,19 @@
           <t>B0FGK5S6YC</t>
         </is>
       </c>
-      <c r="D2395" t="inlineStr"/>
-      <c r="E2395" t="inlineStr"/>
+      <c r="D2395" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2395" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75080,11 +77072,19 @@
           <t>B0FGXTQMLG</t>
         </is>
       </c>
-      <c r="D2396" t="inlineStr"/>
-      <c r="E2396" t="inlineStr"/>
+      <c r="D2396" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="E2396" t="inlineStr">
+        <is>
+          <t>判定不能</t>
+        </is>
+      </c>
       <c r="F2396" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75104,11 +77104,19 @@
           <t>B0FGXZ6JSK</t>
         </is>
       </c>
-      <c r="D2397" t="inlineStr"/>
-      <c r="E2397" t="inlineStr"/>
+      <c r="D2397" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2397" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75128,11 +77136,19 @@
           <t>B0FGZ45QLL</t>
         </is>
       </c>
-      <c r="D2398" t="inlineStr"/>
-      <c r="E2398" t="inlineStr"/>
+      <c r="D2398" t="inlineStr">
+        <is>
+          <t>形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2398" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75152,11 +77168,19 @@
           <t>B0FH22FK3N</t>
         </is>
       </c>
-      <c r="D2399" t="inlineStr"/>
-      <c r="E2399" t="inlineStr"/>
+      <c r="D2399" t="inlineStr">
+        <is>
+          <t>KINGRID</t>
+        </is>
+      </c>
+      <c r="E2399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2399" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -75176,11 +77200,19 @@
           <t>B0FH23PBK2</t>
         </is>
       </c>
-      <c r="D2400" t="inlineStr"/>
-      <c r="E2400" t="inlineStr"/>
+      <c r="D2400" t="inlineStr">
+        <is>
+          <t>ヴァリアス (アーティスト), - (演奏, 作曲) 形式: CD</t>
+        </is>
+      </c>
+      <c r="E2400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2400" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75200,11 +77232,19 @@
           <t>B0FH24HG8N</t>
         </is>
       </c>
-      <c r="D2401" t="inlineStr"/>
-      <c r="E2401" t="inlineStr"/>
+      <c r="D2401" t="inlineStr">
+        <is>
+          <t>ADVINCI</t>
+        </is>
+      </c>
+      <c r="E2401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2401" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -75224,11 +77264,19 @@
           <t>B0FH24W7DP</t>
         </is>
       </c>
-      <c r="D2402" t="inlineStr"/>
-      <c r="E2402" t="inlineStr"/>
+      <c r="D2402" t="inlineStr">
+        <is>
+          <t>ヴァリアス (アーティスト), - (演奏, 作曲) 形式: CD</t>
+        </is>
+      </c>
+      <c r="E2402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2402" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75248,11 +77296,19 @@
           <t>B0FH5HN42T</t>
         </is>
       </c>
-      <c r="D2403" t="inlineStr"/>
-      <c r="E2403" t="inlineStr"/>
+      <c r="D2403" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2403" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75272,11 +77328,19 @@
           <t>B0FH5JKQX9</t>
         </is>
       </c>
-      <c r="D2404" t="inlineStr"/>
-      <c r="E2404" t="inlineStr"/>
+      <c r="D2404" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2404" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75296,11 +77360,19 @@
           <t>B0FH5LF1M2</t>
         </is>
       </c>
-      <c r="D2405" t="inlineStr"/>
-      <c r="E2405" t="inlineStr"/>
+      <c r="D2405" t="inlineStr">
+        <is>
+          <t>Moodymann 形式: LP Record</t>
+        </is>
+      </c>
+      <c r="E2405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2405" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75320,11 +77392,19 @@
           <t>B0FH6S9KVB</t>
         </is>
       </c>
-      <c r="D2406" t="inlineStr"/>
-      <c r="E2406" t="inlineStr"/>
+      <c r="D2406" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2406" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75344,11 +77424,19 @@
           <t>B0FH6XH1NB</t>
         </is>
       </c>
-      <c r="D2407" t="inlineStr"/>
-      <c r="E2407" t="inlineStr"/>
+      <c r="D2407" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2407" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75368,11 +77456,19 @@
           <t>B0FH6ZG6NH</t>
         </is>
       </c>
-      <c r="D2408" t="inlineStr"/>
-      <c r="E2408" t="inlineStr"/>
+      <c r="D2408" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2408" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75392,11 +77488,19 @@
           <t>B0FH79QJKS</t>
         </is>
       </c>
-      <c r="D2409" t="inlineStr"/>
-      <c r="E2409" t="inlineStr"/>
+      <c r="D2409" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2409" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75416,11 +77520,19 @@
           <t>B0FH7B9X5F</t>
         </is>
       </c>
-      <c r="D2410" t="inlineStr"/>
-      <c r="E2410" t="inlineStr"/>
+      <c r="D2410" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2410" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75440,11 +77552,19 @@
           <t>B0FH9BL137</t>
         </is>
       </c>
-      <c r="D2411" t="inlineStr"/>
-      <c r="E2411" t="inlineStr"/>
+      <c r="D2411" t="inlineStr">
+        <is>
+          <t>ハズブロ(HASBRO)</t>
+        </is>
+      </c>
+      <c r="E2411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2411" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75464,11 +77584,19 @@
           <t>B0FH9Z4N3M</t>
         </is>
       </c>
-      <c r="D2412" t="inlineStr"/>
-      <c r="E2412" t="inlineStr"/>
+      <c r="D2412" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2412" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75488,11 +77616,19 @@
           <t>B0FHB1KYSF</t>
         </is>
       </c>
-      <c r="D2413" t="inlineStr"/>
-      <c r="E2413" t="inlineStr"/>
+      <c r="D2413" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2413" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75512,11 +77648,19 @@
           <t>B0FHD4KPYN</t>
         </is>
       </c>
-      <c r="D2414" t="inlineStr"/>
-      <c r="E2414" t="inlineStr"/>
+      <c r="D2414" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2414" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75536,11 +77680,19 @@
           <t>B0FHD99ZR3</t>
         </is>
       </c>
-      <c r="D2415" t="inlineStr"/>
-      <c r="E2415" t="inlineStr"/>
+      <c r="D2415" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2415" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75560,11 +77712,19 @@
           <t>B0FHDBCS2B</t>
         </is>
       </c>
-      <c r="D2416" t="inlineStr"/>
-      <c r="E2416" t="inlineStr"/>
+      <c r="D2416" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2416" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75584,11 +77744,19 @@
           <t>B0FHH8X869</t>
         </is>
       </c>
-      <c r="D2417" t="inlineStr"/>
-      <c r="E2417" t="inlineStr"/>
+      <c r="D2417" t="inlineStr">
+        <is>
+          <t>TM NETWORK (出演) 形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2417" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75608,11 +77776,19 @@
           <t>B0FHJMJCRL</t>
         </is>
       </c>
-      <c r="D2418" t="inlineStr"/>
-      <c r="E2418" t="inlineStr"/>
+      <c r="D2418" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2418" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75632,11 +77808,19 @@
           <t>B0FHKSFRBF</t>
         </is>
       </c>
-      <c r="D2419" t="inlineStr"/>
-      <c r="E2419" t="inlineStr"/>
+      <c r="D2419" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2419" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75656,11 +77840,19 @@
           <t>B0FHKTYXK9</t>
         </is>
       </c>
-      <c r="D2420" t="inlineStr"/>
-      <c r="E2420" t="inlineStr"/>
+      <c r="D2420" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2420" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75680,11 +77872,19 @@
           <t>B0FHKWG97P</t>
         </is>
       </c>
-      <c r="D2421" t="inlineStr"/>
-      <c r="E2421" t="inlineStr"/>
+      <c r="D2421" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2421" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75704,11 +77904,19 @@
           <t>B0FHQ2H52W</t>
         </is>
       </c>
-      <c r="D2422" t="inlineStr"/>
-      <c r="E2422" t="inlineStr"/>
+      <c r="D2422" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2422" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75728,11 +77936,19 @@
           <t>B0FHQ6MK4S</t>
         </is>
       </c>
-      <c r="D2423" t="inlineStr"/>
-      <c r="E2423" t="inlineStr"/>
+      <c r="D2423" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2423" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75752,11 +77968,19 @@
           <t>B0FHQ849PM</t>
         </is>
       </c>
-      <c r="D2424" t="inlineStr"/>
-      <c r="E2424" t="inlineStr"/>
+      <c r="D2424" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2424" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75776,11 +78000,19 @@
           <t>B0FHVJ65PK</t>
         </is>
       </c>
-      <c r="D2425" t="inlineStr"/>
-      <c r="E2425" t="inlineStr"/>
+      <c r="D2425" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2425" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75800,11 +78032,19 @@
           <t>B0FHVNWBXT</t>
         </is>
       </c>
-      <c r="D2426" t="inlineStr"/>
-      <c r="E2426" t="inlineStr"/>
+      <c r="D2426" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2426" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75824,11 +78064,19 @@
           <t>B0FHW7K4YN</t>
         </is>
       </c>
-      <c r="D2427" t="inlineStr"/>
-      <c r="E2427" t="inlineStr"/>
+      <c r="D2427" t="inlineStr">
+        <is>
+          <t>XlamV (出演) 形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2427" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75848,11 +78096,19 @@
           <t>B0FHZHTTHS</t>
         </is>
       </c>
-      <c r="D2428" t="inlineStr"/>
-      <c r="E2428" t="inlineStr"/>
+      <c r="D2428" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2428" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75872,11 +78128,19 @@
           <t>B0FHZTWQ6Z</t>
         </is>
       </c>
-      <c r="D2429" t="inlineStr"/>
-      <c r="E2429" t="inlineStr"/>
+      <c r="D2429" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2429" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75896,11 +78160,19 @@
           <t>B0FJ19HQYQ</t>
         </is>
       </c>
-      <c r="D2430" t="inlineStr"/>
-      <c r="E2430" t="inlineStr"/>
+      <c r="D2430" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2430" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75920,11 +78192,19 @@
           <t>B0FJ1D23T2</t>
         </is>
       </c>
-      <c r="D2431" t="inlineStr"/>
-      <c r="E2431" t="inlineStr"/>
+      <c r="D2431" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2431" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75944,11 +78224,19 @@
           <t>B0FJ1FSR7G</t>
         </is>
       </c>
-      <c r="D2432" t="inlineStr"/>
-      <c r="E2432" t="inlineStr"/>
+      <c r="D2432" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2432" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75968,11 +78256,19 @@
           <t>B0FJ1SRF2R</t>
         </is>
       </c>
-      <c r="D2433" t="inlineStr"/>
-      <c r="E2433" t="inlineStr"/>
+      <c r="D2433" t="inlineStr">
+        <is>
+          <t>阿部顕嵐 (出演, プロデュース) 形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2433" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -75992,11 +78288,19 @@
           <t>B0FJ1VN5TH</t>
         </is>
       </c>
-      <c r="D2434" t="inlineStr"/>
-      <c r="E2434" t="inlineStr"/>
+      <c r="D2434" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="E2434" t="inlineStr">
+        <is>
+          <t>判定不能</t>
+        </is>
+      </c>
       <c r="F2434" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -76016,11 +78320,19 @@
           <t>B0FJ623QQR</t>
         </is>
       </c>
-      <c r="D2435" t="inlineStr"/>
-      <c r="E2435" t="inlineStr"/>
+      <c r="D2435" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2435" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -76040,11 +78352,19 @@
           <t>B0FJ64GXTX</t>
         </is>
       </c>
-      <c r="D2436" t="inlineStr"/>
-      <c r="E2436" t="inlineStr"/>
+      <c r="D2436" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2436" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -76064,11 +78384,19 @@
           <t>B0FJ66D92V</t>
         </is>
       </c>
-      <c r="D2437" t="inlineStr"/>
-      <c r="E2437" t="inlineStr"/>
+      <c r="D2437" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2437" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -76088,11 +78416,19 @@
           <t>B0FJ68MYBN</t>
         </is>
       </c>
-      <c r="D2438" t="inlineStr"/>
-      <c r="E2438" t="inlineStr"/>
+      <c r="D2438" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2438" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -76112,11 +78448,19 @@
           <t>B0FJ6HQFV6</t>
         </is>
       </c>
-      <c r="D2439" t="inlineStr"/>
-      <c r="E2439" t="inlineStr"/>
+      <c r="D2439" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2439" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -76136,11 +78480,19 @@
           <t>B0FJ6J3WF7</t>
         </is>
       </c>
-      <c r="D2440" t="inlineStr"/>
-      <c r="E2440" t="inlineStr"/>
+      <c r="D2440" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2440" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -76160,11 +78512,19 @@
           <t>B0FJ73TZ4D</t>
         </is>
       </c>
-      <c r="D2441" t="inlineStr"/>
-      <c r="E2441" t="inlineStr"/>
+      <c r="D2441" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2441" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -76184,11 +78544,19 @@
           <t>B0FJ75699G</t>
         </is>
       </c>
-      <c r="D2442" t="inlineStr"/>
-      <c r="E2442" t="inlineStr"/>
+      <c r="D2442" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2442" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -76208,11 +78576,19 @@
           <t>B0FJ763PBT</t>
         </is>
       </c>
-      <c r="D2443" t="inlineStr"/>
-      <c r="E2443" t="inlineStr"/>
+      <c r="D2443" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2443" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -76232,11 +78608,19 @@
           <t>B0FJ77HVGX</t>
         </is>
       </c>
-      <c r="D2444" t="inlineStr"/>
-      <c r="E2444" t="inlineStr"/>
+      <c r="D2444" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2444" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -76256,11 +78640,19 @@
           <t>B0FJ77K7JS</t>
         </is>
       </c>
-      <c r="D2445" t="inlineStr"/>
-      <c r="E2445" t="inlineStr"/>
+      <c r="D2445" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2445" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -76280,11 +78672,19 @@
           <t>B0FJ77KLS3</t>
         </is>
       </c>
-      <c r="D2446" t="inlineStr"/>
-      <c r="E2446" t="inlineStr"/>
+      <c r="D2446" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2446" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -76304,11 +78704,19 @@
           <t>B0FJ783KTY</t>
         </is>
       </c>
-      <c r="D2447" t="inlineStr"/>
-      <c r="E2447" t="inlineStr"/>
+      <c r="D2447" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2447" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2447" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -76328,11 +78736,19 @@
           <t>B0FJ786X26</t>
         </is>
       </c>
-      <c r="D2448" t="inlineStr"/>
-      <c r="E2448" t="inlineStr"/>
+      <c r="D2448" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2448" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -76352,11 +78768,19 @@
           <t>B0FJ78FPSV</t>
         </is>
       </c>
-      <c r="D2449" t="inlineStr"/>
-      <c r="E2449" t="inlineStr"/>
+      <c r="D2449" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2449" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -76376,11 +78800,19 @@
           <t>B0FJ7DW26W</t>
         </is>
       </c>
-      <c r="D2450" t="inlineStr"/>
-      <c r="E2450" t="inlineStr"/>
+      <c r="D2450" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2450" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -76400,11 +78832,19 @@
           <t>B0FJ7JJY72</t>
         </is>
       </c>
-      <c r="D2451" t="inlineStr"/>
-      <c r="E2451" t="inlineStr"/>
+      <c r="D2451" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2451" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -76424,11 +78864,19 @@
           <t>B0FJFT29SF</t>
         </is>
       </c>
-      <c r="D2452" t="inlineStr"/>
-      <c r="E2452" t="inlineStr"/>
+      <c r="D2452" t="inlineStr">
+        <is>
+          <t>IQUNIX</t>
+        </is>
+      </c>
+      <c r="E2452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2452" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -76448,11 +78896,19 @@
           <t>B0FJFVZ9P4</t>
         </is>
       </c>
-      <c r="D2453" t="inlineStr"/>
-      <c r="E2453" t="inlineStr"/>
+      <c r="D2453" t="inlineStr">
+        <is>
+          <t>IQUNIX</t>
+        </is>
+      </c>
+      <c r="E2453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2453" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -76472,11 +78928,19 @@
           <t>B0FJFY5JBY</t>
         </is>
       </c>
-      <c r="D2454" t="inlineStr"/>
-      <c r="E2454" t="inlineStr"/>
+      <c r="D2454" t="inlineStr">
+        <is>
+          <t>IQUNIX</t>
+        </is>
+      </c>
+      <c r="E2454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2454" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -76496,11 +78960,19 @@
           <t>B0FJKYRR1S</t>
         </is>
       </c>
-      <c r="D2455" t="inlineStr"/>
-      <c r="E2455" t="inlineStr"/>
+      <c r="D2455" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2455" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -76520,11 +78992,19 @@
           <t>B0FJL496NQ</t>
         </is>
       </c>
-      <c r="D2456" t="inlineStr"/>
-      <c r="E2456" t="inlineStr"/>
+      <c r="D2456" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2456" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -76544,11 +79024,19 @@
           <t>B0FJL5HWB8</t>
         </is>
       </c>
-      <c r="D2457" t="inlineStr"/>
-      <c r="E2457" t="inlineStr"/>
+      <c r="D2457" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2457" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -76568,11 +79056,19 @@
           <t>B0FJM3HXC2</t>
         </is>
       </c>
-      <c r="D2458" t="inlineStr"/>
-      <c r="E2458" t="inlineStr"/>
+      <c r="D2458" t="inlineStr">
+        <is>
+          <t>TUDOLP</t>
+        </is>
+      </c>
+      <c r="E2458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2458" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -76592,11 +79088,19 @@
           <t>B0FJM56J72</t>
         </is>
       </c>
-      <c r="D2459" t="inlineStr"/>
-      <c r="E2459" t="inlineStr"/>
+      <c r="D2459" t="inlineStr">
+        <is>
+          <t>ココグルメ</t>
+        </is>
+      </c>
+      <c r="E2459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2459" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -76616,11 +79120,19 @@
           <t>B0FJM5RGRL</t>
         </is>
       </c>
-      <c r="D2460" t="inlineStr"/>
-      <c r="E2460" t="inlineStr"/>
+      <c r="D2460" t="inlineStr">
+        <is>
+          <t>ココグルメ</t>
+        </is>
+      </c>
+      <c r="E2460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2460" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -76640,11 +79152,19 @@
           <t>B0FJR6GKLY</t>
         </is>
       </c>
-      <c r="D2461" t="inlineStr"/>
-      <c r="E2461" t="inlineStr"/>
+      <c r="D2461" t="inlineStr">
+        <is>
+          <t>丘山晴己　他 (出演) 形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2461" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -76664,11 +79184,19 @@
           <t>B0FJRN4Q8C</t>
         </is>
       </c>
-      <c r="D2462" t="inlineStr"/>
-      <c r="E2462" t="inlineStr"/>
+      <c r="D2462" t="inlineStr">
+        <is>
+          <t>バンダイナムコフィルムワークス (出演) 形式: DVD</t>
+        </is>
+      </c>
+      <c r="E2462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2462" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -76688,11 +79216,19 @@
           <t>B0FJSG1P2T</t>
         </is>
       </c>
-      <c r="D2463" t="inlineStr"/>
-      <c r="E2463" t="inlineStr"/>
+      <c r="D2463" t="inlineStr">
+        <is>
+          <t>LORIEN TESTARD (アーティスト), - (作曲, 演奏) 形式: LP Record</t>
+        </is>
+      </c>
+      <c r="E2463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2463" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -76712,11 +79248,19 @@
           <t>B0FJSG651V</t>
         </is>
       </c>
-      <c r="D2464" t="inlineStr"/>
-      <c r="E2464" t="inlineStr"/>
+      <c r="D2464" t="inlineStr">
+        <is>
+          <t>Lorien Testard (アーティスト) 形式: LP Record</t>
+        </is>
+      </c>
+      <c r="E2464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2464" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -76736,11 +79280,19 @@
           <t>B0FJVG7VJR</t>
         </is>
       </c>
-      <c r="D2465" t="inlineStr"/>
-      <c r="E2465" t="inlineStr"/>
+      <c r="D2465" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="E2465" t="inlineStr">
+        <is>
+          <t>判定不能</t>
+        </is>
+      </c>
       <c r="F2465" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -76760,11 +79312,19 @@
           <t>B0FJWGL1W7</t>
         </is>
       </c>
-      <c r="D2466" t="inlineStr"/>
-      <c r="E2466" t="inlineStr"/>
+      <c r="D2466" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2466" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -76784,11 +79344,19 @@
           <t>B0FJWVJN2S</t>
         </is>
       </c>
-      <c r="D2467" t="inlineStr"/>
-      <c r="E2467" t="inlineStr"/>
+      <c r="D2467" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2467" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -76808,11 +79376,19 @@
           <t>B0FK91TKJH</t>
         </is>
       </c>
-      <c r="D2468" t="inlineStr"/>
-      <c r="E2468" t="inlineStr"/>
+      <c r="D2468" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2468" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -76832,11 +79408,19 @@
           <t>B0FK973XPR</t>
         </is>
       </c>
-      <c r="D2469" t="inlineStr"/>
-      <c r="E2469" t="inlineStr"/>
+      <c r="D2469" t="inlineStr">
+        <is>
+          <t>HanaUly</t>
+        </is>
+      </c>
+      <c r="E2469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2469" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -76856,11 +79440,19 @@
           <t>B0FK9JLBQS</t>
         </is>
       </c>
-      <c r="D2470" t="inlineStr"/>
-      <c r="E2470" t="inlineStr"/>
+      <c r="D2470" t="inlineStr">
+        <is>
+          <t>Sodola</t>
+        </is>
+      </c>
+      <c r="E2470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2470" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -76880,11 +79472,19 @@
           <t>B0FK9N9PJF</t>
         </is>
       </c>
-      <c r="D2471" t="inlineStr"/>
-      <c r="E2471" t="inlineStr"/>
+      <c r="D2471" t="inlineStr">
+        <is>
+          <t>HanaUly</t>
+        </is>
+      </c>
+      <c r="E2471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2471" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -76904,11 +79504,19 @@
           <t>B0FKB28RCW</t>
         </is>
       </c>
-      <c r="D2472" t="inlineStr"/>
-      <c r="E2472" t="inlineStr"/>
+      <c r="D2472" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2472" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2472" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -76928,11 +79536,19 @@
           <t>B0FKFMC331</t>
         </is>
       </c>
-      <c r="D2473" t="inlineStr"/>
-      <c r="E2473" t="inlineStr"/>
+      <c r="D2473" t="inlineStr">
+        <is>
+          <t>ぶるーぷらむ</t>
+        </is>
+      </c>
+      <c r="E2473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2473" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -76952,11 +79568,19 @@
           <t>B0FKFMSL8T</t>
         </is>
       </c>
-      <c r="D2474" t="inlineStr"/>
-      <c r="E2474" t="inlineStr"/>
+      <c r="D2474" t="inlineStr">
+        <is>
+          <t>ZPUJIU</t>
+        </is>
+      </c>
+      <c r="E2474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2474" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -76976,11 +79600,19 @@
           <t>B0FKFNG1WQ</t>
         </is>
       </c>
-      <c r="D2475" t="inlineStr"/>
-      <c r="E2475" t="inlineStr"/>
+      <c r="D2475" t="inlineStr">
+        <is>
+          <t>ZPUJIU</t>
+        </is>
+      </c>
+      <c r="E2475" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2475" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -77000,11 +79632,19 @@
           <t>B0FKFNJGCV</t>
         </is>
       </c>
-      <c r="D2476" t="inlineStr"/>
-      <c r="E2476" t="inlineStr"/>
+      <c r="D2476" t="inlineStr">
+        <is>
+          <t>ZPUJIU</t>
+        </is>
+      </c>
+      <c r="E2476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2476" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -77024,11 +79664,19 @@
           <t>B0FKGR7S9H</t>
         </is>
       </c>
-      <c r="D2477" t="inlineStr"/>
-      <c r="E2477" t="inlineStr"/>
+      <c r="D2477" t="inlineStr">
+        <is>
+          <t>花華やぐも、散るは密やか (出演) 形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2477" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -77048,11 +79696,19 @@
           <t>B0FKGRFCCW</t>
         </is>
       </c>
-      <c r="D2478" t="inlineStr"/>
-      <c r="E2478" t="inlineStr"/>
+      <c r="D2478" t="inlineStr">
+        <is>
+          <t>花華やぐも、散るは密やか (出演) 形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2478" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -77072,11 +79728,19 @@
           <t>B0FKNFBSGH</t>
         </is>
       </c>
-      <c r="D2479" t="inlineStr"/>
-      <c r="E2479" t="inlineStr"/>
+      <c r="D2479" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2479" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -77096,11 +79760,19 @@
           <t>B0FKNG6YGV</t>
         </is>
       </c>
-      <c r="D2480" t="inlineStr"/>
-      <c r="E2480" t="inlineStr"/>
+      <c r="D2480" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2480" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -77120,11 +79792,19 @@
           <t>B0FKNH1Y4C</t>
         </is>
       </c>
-      <c r="D2481" t="inlineStr"/>
-      <c r="E2481" t="inlineStr"/>
+      <c r="D2481" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2481" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -77144,11 +79824,19 @@
           <t>B0FKNK1Q6D</t>
         </is>
       </c>
-      <c r="D2482" t="inlineStr"/>
-      <c r="E2482" t="inlineStr"/>
+      <c r="D2482" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2482" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -77168,11 +79856,19 @@
           <t>B0FKNK8SMZ</t>
         </is>
       </c>
-      <c r="D2483" t="inlineStr"/>
-      <c r="E2483" t="inlineStr"/>
+      <c r="D2483" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2483" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -77192,11 +79888,19 @@
           <t>B0FKNKTNPY</t>
         </is>
       </c>
-      <c r="D2484" t="inlineStr"/>
-      <c r="E2484" t="inlineStr"/>
+      <c r="D2484" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2484" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -77216,11 +79920,19 @@
           <t>B0FKNLF4TF</t>
         </is>
       </c>
-      <c r="D2485" t="inlineStr"/>
-      <c r="E2485" t="inlineStr"/>
+      <c r="D2485" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2485" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -77240,11 +79952,19 @@
           <t>B0FKNPZ8X7</t>
         </is>
       </c>
-      <c r="D2486" t="inlineStr"/>
-      <c r="E2486" t="inlineStr"/>
+      <c r="D2486" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2486" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -77264,11 +79984,19 @@
           <t>B0FKNZ478X</t>
         </is>
       </c>
-      <c r="D2487" t="inlineStr"/>
-      <c r="E2487" t="inlineStr"/>
+      <c r="D2487" t="inlineStr">
+        <is>
+          <t>島谷ひとみ 形式: CD</t>
+        </is>
+      </c>
+      <c r="E2487" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2487" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -77288,11 +80016,19 @@
           <t>B0FKR98KK1</t>
         </is>
       </c>
-      <c r="D2488" t="inlineStr"/>
-      <c r="E2488" t="inlineStr"/>
+      <c r="D2488" t="inlineStr">
+        <is>
+          <t>SKYFLY（スカイフライ）</t>
+        </is>
+      </c>
+      <c r="E2488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2488" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -77312,11 +80048,19 @@
           <t>B0FKRBHZ8J</t>
         </is>
       </c>
-      <c r="D2489" t="inlineStr"/>
-      <c r="E2489" t="inlineStr"/>
+      <c r="D2489" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2489" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2489" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -77336,11 +80080,19 @@
           <t>B0FKRHXCV2</t>
         </is>
       </c>
-      <c r="D2490" t="inlineStr"/>
-      <c r="E2490" t="inlineStr"/>
+      <c r="D2490" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2490" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -77360,11 +80112,19 @@
           <t>B0FKRLJQDN</t>
         </is>
       </c>
-      <c r="D2491" t="inlineStr"/>
-      <c r="E2491" t="inlineStr"/>
+      <c r="D2491" t="inlineStr">
+        <is>
+          <t>SKYFLY（スカイフライ）</t>
+        </is>
+      </c>
+      <c r="E2491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2491" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -77384,11 +80144,19 @@
           <t>B0FKRY4CD6</t>
         </is>
       </c>
-      <c r="D2492" t="inlineStr"/>
-      <c r="E2492" t="inlineStr"/>
+      <c r="D2492" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2492" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -77408,11 +80176,19 @@
           <t>B0FKRYTBR4</t>
         </is>
       </c>
-      <c r="D2493" t="inlineStr"/>
-      <c r="E2493" t="inlineStr"/>
+      <c r="D2493" t="inlineStr">
+        <is>
+          <t>SKYFLY（スカイフライ）</t>
+        </is>
+      </c>
+      <c r="E2493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2493" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>N Recovered (-)</t>
         </is>
       </c>
     </row>
@@ -77432,11 +80208,19 @@
           <t>B0FKSBJPQ2</t>
         </is>
       </c>
-      <c r="D2494" t="inlineStr"/>
-      <c r="E2494" t="inlineStr"/>
+      <c r="D2494" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2494" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2494" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -77456,11 +80240,19 @@
           <t>B0FKT6WWS4</t>
         </is>
       </c>
-      <c r="D2495" t="inlineStr"/>
-      <c r="E2495" t="inlineStr"/>
+      <c r="D2495" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2495" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -77480,11 +80272,19 @@
           <t>B0FKXPGYTZ</t>
         </is>
       </c>
-      <c r="D2496" t="inlineStr"/>
-      <c r="E2496" t="inlineStr"/>
+      <c r="D2496" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2496" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -77504,11 +80304,19 @@
           <t>B0FKXZWFMX</t>
         </is>
       </c>
-      <c r="D2497" t="inlineStr"/>
-      <c r="E2497" t="inlineStr"/>
+      <c r="D2497" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2497" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2497" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -77528,11 +80336,19 @@
           <t>B0FKY13TGL</t>
         </is>
       </c>
-      <c r="D2498" t="inlineStr"/>
-      <c r="E2498" t="inlineStr"/>
+      <c r="D2498" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2498" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2498" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -77552,11 +80368,19 @@
           <t>B0FKY4RTD6</t>
         </is>
       </c>
-      <c r="D2499" t="inlineStr"/>
-      <c r="E2499" t="inlineStr"/>
+      <c r="D2499" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2499" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2499" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -77576,11 +80400,19 @@
           <t>B0FKY821WH</t>
         </is>
       </c>
-      <c r="D2500" t="inlineStr"/>
-      <c r="E2500" t="inlineStr"/>
+      <c r="D2500" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2500" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2500" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -77600,11 +80432,19 @@
           <t>B0FKYW8KH4</t>
         </is>
       </c>
-      <c r="D2501" t="inlineStr"/>
-      <c r="E2501" t="inlineStr"/>
+      <c r="D2501" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2501" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2501" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -77624,11 +80464,19 @@
           <t>B0FKYWFPKQ</t>
         </is>
       </c>
-      <c r="D2502" t="inlineStr"/>
-      <c r="E2502" t="inlineStr"/>
+      <c r="D2502" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="E2502" t="inlineStr">
+        <is>
+          <t>判定不能</t>
+        </is>
+      </c>
       <c r="F2502" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -77648,11 +80496,19 @@
           <t>B0FKZ9PJWD</t>
         </is>
       </c>
-      <c r="D2503" t="inlineStr"/>
-      <c r="E2503" t="inlineStr"/>
+      <c r="D2503" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2503" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2503" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -77672,11 +80528,19 @@
           <t>B0FKZ9WPCY</t>
         </is>
       </c>
-      <c r="D2504" t="inlineStr"/>
-      <c r="E2504" t="inlineStr"/>
+      <c r="D2504" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2504" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2504" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -77696,11 +80560,19 @@
           <t>B0FKZB1J8F</t>
         </is>
       </c>
-      <c r="D2505" t="inlineStr"/>
-      <c r="E2505" t="inlineStr"/>
+      <c r="D2505" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2505" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2505" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -77720,11 +80592,19 @@
           <t>B0FKZD1T56</t>
         </is>
       </c>
-      <c r="D2506" t="inlineStr"/>
-      <c r="E2506" t="inlineStr"/>
+      <c r="D2506" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2506" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2506" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -77744,11 +80624,19 @@
           <t>B0FL1QQWKL</t>
         </is>
       </c>
-      <c r="D2507" t="inlineStr"/>
-      <c r="E2507" t="inlineStr"/>
+      <c r="D2507" t="inlineStr">
+        <is>
+          <t>NEWS (出演) 形式: DVD</t>
+        </is>
+      </c>
+      <c r="E2507" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2507" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -77768,11 +80656,19 @@
           <t>B0FL1R98SH</t>
         </is>
       </c>
-      <c r="D2508" t="inlineStr"/>
-      <c r="E2508" t="inlineStr"/>
+      <c r="D2508" t="inlineStr">
+        <is>
+          <t>堂本光一 形式: CD</t>
+        </is>
+      </c>
+      <c r="E2508" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2508" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -77792,11 +80688,19 @@
           <t>B0FL1S5FRC</t>
         </is>
       </c>
-      <c r="D2509" t="inlineStr"/>
-      <c r="E2509" t="inlineStr"/>
+      <c r="D2509" t="inlineStr">
+        <is>
+          <t>NEWS (出演) 形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2509" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -77816,11 +80720,19 @@
           <t>B0FL22BKWN</t>
         </is>
       </c>
-      <c r="D2510" t="inlineStr"/>
-      <c r="E2510" t="inlineStr"/>
+      <c r="D2510" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2510" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2510" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -77840,11 +80752,19 @@
           <t>B0FL23JR4H</t>
         </is>
       </c>
-      <c r="D2511" t="inlineStr"/>
-      <c r="E2511" t="inlineStr"/>
+      <c r="D2511" t="inlineStr">
+        <is>
+          <t>金子修介 (監督), 村石宏實 (監督), 青山草太 (出演), 形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2511" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -77864,11 +80784,19 @@
           <t>B0FL245F5Z</t>
         </is>
       </c>
-      <c r="D2512" t="inlineStr"/>
-      <c r="E2512" t="inlineStr"/>
+      <c r="D2512" t="inlineStr">
+        <is>
+          <t>金子修介 (監督), 村石宏實 (監督), 青山草太 (出演), 形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2512" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -77888,11 +80816,19 @@
           <t>B0FL73MNMC</t>
         </is>
       </c>
-      <c r="D2513" t="inlineStr"/>
-      <c r="E2513" t="inlineStr"/>
+      <c r="D2513" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2513" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -77912,11 +80848,19 @@
           <t>B0FL7L2FXB</t>
         </is>
       </c>
-      <c r="D2514" t="inlineStr"/>
-      <c r="E2514" t="inlineStr"/>
+      <c r="D2514" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2514" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -77936,11 +80880,19 @@
           <t>B0FL7M8M9N</t>
         </is>
       </c>
-      <c r="D2515" t="inlineStr"/>
-      <c r="E2515" t="inlineStr"/>
+      <c r="D2515" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2515" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -77960,11 +80912,19 @@
           <t>B0FL7MTY3M</t>
         </is>
       </c>
-      <c r="D2516" t="inlineStr"/>
-      <c r="E2516" t="inlineStr"/>
+      <c r="D2516" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2516" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -77984,11 +80944,19 @@
           <t>B0FLC2VJW9</t>
         </is>
       </c>
-      <c r="D2517" t="inlineStr"/>
-      <c r="E2517" t="inlineStr"/>
+      <c r="D2517" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2517" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="F2517" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78008,11 +80976,19 @@
           <t>B0FLDBHF2K</t>
         </is>
       </c>
-      <c r="D2518" t="inlineStr"/>
-      <c r="E2518" t="inlineStr"/>
+      <c r="D2518" t="inlineStr">
+        <is>
+          <t>björk (出演) 形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2518" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78032,11 +81008,19 @@
           <t>B0FLDFYRRM</t>
         </is>
       </c>
-      <c r="D2519" t="inlineStr"/>
-      <c r="E2519" t="inlineStr"/>
+      <c r="D2519" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2519" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78056,11 +81040,19 @@
           <t>B0FLDHBBWD</t>
         </is>
       </c>
-      <c r="D2520" t="inlineStr"/>
-      <c r="E2520" t="inlineStr"/>
+      <c r="D2520" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="E2520" t="inlineStr">
+        <is>
+          <t>判定不能</t>
+        </is>
+      </c>
       <c r="F2520" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78080,11 +81072,19 @@
           <t>B0FLDHK2W6</t>
         </is>
       </c>
-      <c r="D2521" t="inlineStr"/>
-      <c r="E2521" t="inlineStr"/>
+      <c r="D2521" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="E2521" t="inlineStr">
+        <is>
+          <t>判定不能</t>
+        </is>
+      </c>
       <c r="F2521" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78104,11 +81104,19 @@
           <t>B0FLDJG7C5</t>
         </is>
       </c>
-      <c r="D2522" t="inlineStr"/>
-      <c r="E2522" t="inlineStr"/>
+      <c r="D2522" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="E2522" t="inlineStr">
+        <is>
+          <t>判定不能</t>
+        </is>
+      </c>
       <c r="F2522" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78128,11 +81136,19 @@
           <t>B0FLDJJ27R</t>
         </is>
       </c>
-      <c r="D2523" t="inlineStr"/>
-      <c r="E2523" t="inlineStr"/>
+      <c r="D2523" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="E2523" t="inlineStr">
+        <is>
+          <t>判定不能</t>
+        </is>
+      </c>
       <c r="F2523" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78152,11 +81168,19 @@
           <t>B0FLDJXFDS</t>
         </is>
       </c>
-      <c r="D2524" t="inlineStr"/>
-      <c r="E2524" t="inlineStr"/>
+      <c r="D2524" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="E2524" t="inlineStr">
+        <is>
+          <t>判定不能</t>
+        </is>
+      </c>
       <c r="F2524" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78176,11 +81200,19 @@
           <t>B0FLDKHD9L</t>
         </is>
       </c>
-      <c r="D2525" t="inlineStr"/>
-      <c r="E2525" t="inlineStr"/>
+      <c r="D2525" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="E2525" t="inlineStr">
+        <is>
+          <t>判定不能</t>
+        </is>
+      </c>
       <c r="F2525" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78200,11 +81232,19 @@
           <t>B0FLDKJYMH</t>
         </is>
       </c>
-      <c r="D2526" t="inlineStr"/>
-      <c r="E2526" t="inlineStr"/>
+      <c r="D2526" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="E2526" t="inlineStr">
+        <is>
+          <t>判定不能</t>
+        </is>
+      </c>
       <c r="F2526" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78224,11 +81264,19 @@
           <t>B0FLDKSJLJ</t>
         </is>
       </c>
-      <c r="D2527" t="inlineStr"/>
-      <c r="E2527" t="inlineStr"/>
+      <c r="D2527" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="E2527" t="inlineStr">
+        <is>
+          <t>判定不能</t>
+        </is>
+      </c>
       <c r="F2527" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78248,11 +81296,19 @@
           <t>B0FLDKYXTB</t>
         </is>
       </c>
-      <c r="D2528" t="inlineStr"/>
-      <c r="E2528" t="inlineStr"/>
+      <c r="D2528" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="E2528" t="inlineStr">
+        <is>
+          <t>判定不能</t>
+        </is>
+      </c>
       <c r="F2528" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78272,11 +81328,19 @@
           <t>B0FLDKZDY5</t>
         </is>
       </c>
-      <c r="D2529" t="inlineStr"/>
-      <c r="E2529" t="inlineStr"/>
+      <c r="D2529" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="E2529" t="inlineStr">
+        <is>
+          <t>判定不能</t>
+        </is>
+      </c>
       <c r="F2529" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78296,11 +81360,19 @@
           <t>B0FLDL2269</t>
         </is>
       </c>
-      <c r="D2530" t="inlineStr"/>
-      <c r="E2530" t="inlineStr"/>
+      <c r="D2530" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="E2530" t="inlineStr">
+        <is>
+          <t>判定不能</t>
+        </is>
+      </c>
       <c r="F2530" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78320,11 +81392,19 @@
           <t>B0FLDL7BS8</t>
         </is>
       </c>
-      <c r="D2531" t="inlineStr"/>
-      <c r="E2531" t="inlineStr"/>
+      <c r="D2531" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="E2531" t="inlineStr">
+        <is>
+          <t>判定不能</t>
+        </is>
+      </c>
       <c r="F2531" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78344,11 +81424,19 @@
           <t>B0FLDLHC4G</t>
         </is>
       </c>
-      <c r="D2532" t="inlineStr"/>
-      <c r="E2532" t="inlineStr"/>
+      <c r="D2532" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2532" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78368,11 +81456,19 @@
           <t>B0FLDLPG57</t>
         </is>
       </c>
-      <c r="D2533" t="inlineStr"/>
-      <c r="E2533" t="inlineStr"/>
+      <c r="D2533" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="E2533" t="inlineStr">
+        <is>
+          <t>判定不能</t>
+        </is>
+      </c>
       <c r="F2533" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78392,11 +81488,19 @@
           <t>B0FLDM2SN3</t>
         </is>
       </c>
-      <c r="D2534" t="inlineStr"/>
-      <c r="E2534" t="inlineStr"/>
+      <c r="D2534" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2534" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78416,11 +81520,19 @@
           <t>B0FLDMH8D8</t>
         </is>
       </c>
-      <c r="D2535" t="inlineStr"/>
-      <c r="E2535" t="inlineStr"/>
+      <c r="D2535" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2535" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78440,11 +81552,19 @@
           <t>B0FLDMLP7H</t>
         </is>
       </c>
-      <c r="D2536" t="inlineStr"/>
-      <c r="E2536" t="inlineStr"/>
+      <c r="D2536" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="E2536" t="inlineStr">
+        <is>
+          <t>判定不能</t>
+        </is>
+      </c>
       <c r="F2536" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78464,11 +81584,19 @@
           <t>B0FLF61J4D</t>
         </is>
       </c>
-      <c r="D2537" t="inlineStr"/>
-      <c r="E2537" t="inlineStr"/>
+      <c r="D2537" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2537" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78488,11 +81616,19 @@
           <t>B0FLF89X8W</t>
         </is>
       </c>
-      <c r="D2538" t="inlineStr"/>
-      <c r="E2538" t="inlineStr"/>
+      <c r="D2538" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2538" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78512,11 +81648,19 @@
           <t>B0FLH3DD1K</t>
         </is>
       </c>
-      <c r="D2539" t="inlineStr"/>
-      <c r="E2539" t="inlineStr"/>
+      <c r="D2539" t="inlineStr">
+        <is>
+          <t>ＢＥ：ＦＩＲＳＴ 形式: CD</t>
+        </is>
+      </c>
+      <c r="E2539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2539" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78536,11 +81680,19 @@
           <t>B0FLH665FJ</t>
         </is>
       </c>
-      <c r="D2540" t="inlineStr"/>
-      <c r="E2540" t="inlineStr"/>
+      <c r="D2540" t="inlineStr">
+        <is>
+          <t>ＢＥ：ＦＩＲＳＴ 形式: CD</t>
+        </is>
+      </c>
+      <c r="E2540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2540" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78560,11 +81712,19 @@
           <t>B0FLJ65X45</t>
         </is>
       </c>
-      <c r="D2541" t="inlineStr"/>
-      <c r="E2541" t="inlineStr"/>
+      <c r="D2541" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2541" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78584,11 +81744,19 @@
           <t>B0FLJGQHNY</t>
         </is>
       </c>
-      <c r="D2542" t="inlineStr"/>
-      <c r="E2542" t="inlineStr"/>
+      <c r="D2542" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2542" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="F2542" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78608,11 +81776,19 @@
           <t>B0FLPL2GYZ</t>
         </is>
       </c>
-      <c r="D2543" t="inlineStr"/>
-      <c r="E2543" t="inlineStr"/>
+      <c r="D2543" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2543" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78632,11 +81808,19 @@
           <t>B0FLPXT4Z7</t>
         </is>
       </c>
-      <c r="D2544" t="inlineStr"/>
-      <c r="E2544" t="inlineStr"/>
+      <c r="D2544" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2544" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78656,11 +81840,19 @@
           <t>B0FLQR77QR</t>
         </is>
       </c>
-      <c r="D2545" t="inlineStr"/>
-      <c r="E2545" t="inlineStr"/>
+      <c r="D2545" t="inlineStr">
+        <is>
+          <t>Frank Zappa (アーティスト) 形式: CD</t>
+        </is>
+      </c>
+      <c r="E2545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2545" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78680,11 +81872,19 @@
           <t>B0FLV6ZFWC</t>
         </is>
       </c>
-      <c r="D2546" t="inlineStr"/>
-      <c r="E2546" t="inlineStr"/>
+      <c r="D2546" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2546" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78704,11 +81904,19 @@
           <t>B0FLXV1XPX</t>
         </is>
       </c>
-      <c r="D2547" t="inlineStr"/>
-      <c r="E2547" t="inlineStr"/>
+      <c r="D2547" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2547" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78728,11 +81936,19 @@
           <t>B0FLXZF1RD</t>
         </is>
       </c>
-      <c r="D2548" t="inlineStr"/>
-      <c r="E2548" t="inlineStr"/>
+      <c r="D2548" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2548" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78752,11 +81968,19 @@
           <t>B0FLYD66HS</t>
         </is>
       </c>
-      <c r="D2549" t="inlineStr"/>
-      <c r="E2549" t="inlineStr"/>
+      <c r="D2549" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2549" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78776,11 +82000,19 @@
           <t>B0FLYG7JHX</t>
         </is>
       </c>
-      <c r="D2550" t="inlineStr"/>
-      <c r="E2550" t="inlineStr"/>
+      <c r="D2550" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2550" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78800,11 +82032,19 @@
           <t>B0FLYHM1CY</t>
         </is>
       </c>
-      <c r="D2551" t="inlineStr"/>
-      <c r="E2551" t="inlineStr"/>
+      <c r="D2551" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2551" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78824,11 +82064,19 @@
           <t>B0FM8QL2C8</t>
         </is>
       </c>
-      <c r="D2552" t="inlineStr"/>
-      <c r="E2552" t="inlineStr"/>
+      <c r="D2552" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2552" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2552" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78848,11 +82096,19 @@
           <t>B0FM8TCVZC</t>
         </is>
       </c>
-      <c r="D2553" t="inlineStr"/>
-      <c r="E2553" t="inlineStr"/>
+      <c r="D2553" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2553" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2553" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78872,11 +82128,19 @@
           <t>B0FM8XBH4R</t>
         </is>
       </c>
-      <c r="D2554" t="inlineStr"/>
-      <c r="E2554" t="inlineStr"/>
+      <c r="D2554" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2554" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2554" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78896,11 +82160,19 @@
           <t>B0FMC62NCK</t>
         </is>
       </c>
-      <c r="D2555" t="inlineStr"/>
-      <c r="E2555" t="inlineStr"/>
+      <c r="D2555" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="E2555" t="inlineStr">
+        <is>
+          <t>判定不能</t>
+        </is>
+      </c>
       <c r="F2555" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78920,11 +82192,19 @@
           <t>B0FMF3ZM3J</t>
         </is>
       </c>
-      <c r="D2556" t="inlineStr"/>
-      <c r="E2556" t="inlineStr"/>
+      <c r="D2556" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2556" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78944,11 +82224,19 @@
           <t>B0FMF6WQ2G</t>
         </is>
       </c>
-      <c r="D2557" t="inlineStr"/>
-      <c r="E2557" t="inlineStr"/>
+      <c r="D2557" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2557" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78968,11 +82256,19 @@
           <t>B0FMK6T3ZF</t>
         </is>
       </c>
-      <c r="D2558" t="inlineStr"/>
-      <c r="E2558" t="inlineStr"/>
+      <c r="D2558" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2558" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -78992,11 +82288,19 @@
           <t>B0FMKBCSQW</t>
         </is>
       </c>
-      <c r="D2559" t="inlineStr"/>
-      <c r="E2559" t="inlineStr"/>
+      <c r="D2559" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2559" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -79016,11 +82320,19 @@
           <t>B0FMN3TFWG</t>
         </is>
       </c>
-      <c r="D2560" t="inlineStr"/>
-      <c r="E2560" t="inlineStr"/>
+      <c r="D2560" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2560" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -79040,11 +82352,19 @@
           <t>B0FMNPLJSP</t>
         </is>
       </c>
-      <c r="D2561" t="inlineStr"/>
-      <c r="E2561" t="inlineStr"/>
+      <c r="D2561" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2561" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -79064,11 +82384,19 @@
           <t>B0FMQZ44LS</t>
         </is>
       </c>
-      <c r="D2562" t="inlineStr"/>
-      <c r="E2562" t="inlineStr"/>
+      <c r="D2562" t="inlineStr">
+        <is>
+          <t>シーナ・イーストン 形式: CD</t>
+        </is>
+      </c>
+      <c r="E2562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2562" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -79088,11 +82416,19 @@
           <t>B0FMR9VSJN</t>
         </is>
       </c>
-      <c r="D2563" t="inlineStr"/>
-      <c r="E2563" t="inlineStr"/>
+      <c r="D2563" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2563" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -79112,11 +82448,19 @@
           <t>B0FMRJ7X8Z</t>
         </is>
       </c>
-      <c r="D2564" t="inlineStr"/>
-      <c r="E2564" t="inlineStr"/>
+      <c r="D2564" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2564" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -79136,11 +82480,19 @@
           <t>B0FMRTKFVN</t>
         </is>
       </c>
-      <c r="D2565" t="inlineStr"/>
-      <c r="E2565" t="inlineStr"/>
+      <c r="D2565" t="inlineStr">
+        <is>
+          <t>松田元太 (出演) 形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2565" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -79160,11 +82512,19 @@
           <t>B0FMXH8ZRS</t>
         </is>
       </c>
-      <c r="D2566" t="inlineStr"/>
-      <c r="E2566" t="inlineStr"/>
+      <c r="D2566" t="inlineStr">
+        <is>
+          <t>取得失敗</t>
+        </is>
+      </c>
+      <c r="E2566" t="inlineStr">
+        <is>
+          <t>判定不能</t>
+        </is>
+      </c>
       <c r="F2566" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -79184,11 +82544,19 @@
           <t>B0FMY7YL8X</t>
         </is>
       </c>
-      <c r="D2567" t="inlineStr"/>
-      <c r="E2567" t="inlineStr"/>
+      <c r="D2567" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2567" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -79208,11 +82576,19 @@
           <t>B0FMY8L2KX</t>
         </is>
       </c>
-      <c r="D2568" t="inlineStr"/>
-      <c r="E2568" t="inlineStr"/>
+      <c r="D2568" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2568" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2568" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -79232,11 +82608,19 @@
           <t>B0FMYD2TD1</t>
         </is>
       </c>
-      <c r="D2569" t="inlineStr"/>
-      <c r="E2569" t="inlineStr"/>
+      <c r="D2569" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2569" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2569" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -79256,11 +82640,19 @@
           <t>B0FMYJJQ6C</t>
         </is>
       </c>
-      <c r="D2570" t="inlineStr"/>
-      <c r="E2570" t="inlineStr"/>
+      <c r="D2570" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2570" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2570" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -79280,11 +82672,19 @@
           <t>B0FMYL5P5Z</t>
         </is>
       </c>
-      <c r="D2571" t="inlineStr"/>
-      <c r="E2571" t="inlineStr"/>
+      <c r="D2571" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2571" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2571" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -79304,11 +82704,19 @@
           <t>B0FMYLXFZP</t>
         </is>
       </c>
-      <c r="D2572" t="inlineStr"/>
-      <c r="E2572" t="inlineStr"/>
+      <c r="D2572" t="inlineStr">
+        <is>
+          <t>丘山晴己　他 (出演) 形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2572" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2572" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -79328,11 +82736,19 @@
           <t>B0FN2QJPJK</t>
         </is>
       </c>
-      <c r="D2573" t="inlineStr"/>
-      <c r="E2573" t="inlineStr"/>
+      <c r="D2573" t="inlineStr">
+        <is>
+          <t>壱百満天原サロメ (出演) 形式: Blu-ray</t>
+        </is>
+      </c>
+      <c r="E2573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2573" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -79352,11 +82768,19 @@
           <t>B0FN356D54</t>
         </is>
       </c>
-      <c r="D2574" t="inlineStr"/>
-      <c r="E2574" t="inlineStr"/>
+      <c r="D2574" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2574" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -79376,11 +82800,19 @@
           <t>B0FN3BDWLL</t>
         </is>
       </c>
-      <c r="D2575" t="inlineStr"/>
-      <c r="E2575" t="inlineStr"/>
+      <c r="D2575" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2575" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
@@ -79400,11 +82832,19 @@
           <t>B0FN3MZVC7</t>
         </is>
       </c>
-      <c r="D2576" t="inlineStr"/>
-      <c r="E2576" t="inlineStr"/>
+      <c r="D2576" t="inlineStr">
+        <is>
+          <t>Amazon Renewed</t>
+        </is>
+      </c>
+      <c r="E2576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F2576" t="inlineStr">
         <is>
-          <t>waiting</t>
+          <t>Mismatch (N maintained)</t>
         </is>
       </c>
     </row>
